--- a/output/version3/test/15-5/MARL/CTDE/RL-RL with EP (+comm)/(RL+RL) test results.xlsx
+++ b/output/version3/test/15-5/MARL/CTDE/RL-RL with EP (+comm)/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>660</v>
+        <v>667</v>
       </c>
       <c r="C2" t="n">
-        <v>658</v>
+        <v>678</v>
       </c>
       <c r="D2" t="n">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="E2" t="n">
-        <v>624</v>
+        <v>723</v>
       </c>
       <c r="F2" t="n">
-        <v>579</v>
+        <v>647</v>
       </c>
       <c r="G2" t="n">
-        <v>610</v>
+        <v>678</v>
       </c>
       <c r="H2" t="n">
-        <v>598</v>
+        <v>669</v>
       </c>
       <c r="I2" t="n">
-        <v>799</v>
+        <v>663</v>
       </c>
       <c r="J2" t="n">
-        <v>610</v>
+        <v>646</v>
       </c>
       <c r="K2" t="n">
-        <v>703</v>
+        <v>657</v>
       </c>
       <c r="L2" t="n">
-        <v>646</v>
+        <v>665.9</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>751</v>
+        <v>728</v>
       </c>
       <c r="C3" t="n">
+        <v>830</v>
+      </c>
+      <c r="D3" t="n">
+        <v>789</v>
+      </c>
+      <c r="E3" t="n">
+        <v>777</v>
+      </c>
+      <c r="F3" t="n">
+        <v>782</v>
+      </c>
+      <c r="G3" t="n">
+        <v>813</v>
+      </c>
+      <c r="H3" t="n">
+        <v>867</v>
+      </c>
+      <c r="I3" t="n">
+        <v>816</v>
+      </c>
+      <c r="J3" t="n">
         <v>785</v>
       </c>
-      <c r="D3" t="n">
-        <v>798</v>
-      </c>
-      <c r="E3" t="n">
-        <v>779</v>
-      </c>
-      <c r="F3" t="n">
-        <v>795</v>
-      </c>
-      <c r="G3" t="n">
+      <c r="K3" t="n">
         <v>784</v>
       </c>
-      <c r="H3" t="n">
-        <v>826</v>
-      </c>
-      <c r="I3" t="n">
-        <v>781</v>
-      </c>
-      <c r="J3" t="n">
-        <v>773</v>
-      </c>
-      <c r="K3" t="n">
-        <v>752</v>
-      </c>
       <c r="L3" t="n">
-        <v>782.4</v>
+        <v>797.1</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>774</v>
+        <v>692</v>
       </c>
       <c r="C4" t="n">
-        <v>771</v>
+        <v>785</v>
       </c>
       <c r="D4" t="n">
-        <v>746</v>
+        <v>762</v>
       </c>
       <c r="E4" t="n">
-        <v>756</v>
+        <v>696</v>
       </c>
       <c r="F4" t="n">
+        <v>742</v>
+      </c>
+      <c r="G4" t="n">
+        <v>755</v>
+      </c>
+      <c r="H4" t="n">
+        <v>699</v>
+      </c>
+      <c r="I4" t="n">
+        <v>754</v>
+      </c>
+      <c r="J4" t="n">
+        <v>733</v>
+      </c>
+      <c r="K4" t="n">
         <v>697</v>
       </c>
-      <c r="G4" t="n">
-        <v>770</v>
-      </c>
-      <c r="H4" t="n">
-        <v>718</v>
-      </c>
-      <c r="I4" t="n">
-        <v>722</v>
-      </c>
-      <c r="J4" t="n">
-        <v>715</v>
-      </c>
-      <c r="K4" t="n">
-        <v>734</v>
-      </c>
       <c r="L4" t="n">
-        <v>740.3</v>
+        <v>731.5</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>781</v>
+        <v>817</v>
       </c>
       <c r="C5" t="n">
-        <v>831</v>
+        <v>928</v>
       </c>
       <c r="D5" t="n">
-        <v>902</v>
+        <v>939</v>
       </c>
       <c r="E5" t="n">
+        <v>820</v>
+      </c>
+      <c r="F5" t="n">
+        <v>932</v>
+      </c>
+      <c r="G5" t="n">
+        <v>917</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1007</v>
+      </c>
+      <c r="I5" t="n">
         <v>916</v>
       </c>
-      <c r="F5" t="n">
-        <v>862</v>
-      </c>
-      <c r="G5" t="n">
-        <v>832</v>
-      </c>
-      <c r="H5" t="n">
-        <v>836</v>
-      </c>
-      <c r="I5" t="n">
-        <v>881</v>
-      </c>
       <c r="J5" t="n">
-        <v>952</v>
+        <v>968</v>
       </c>
       <c r="K5" t="n">
-        <v>812</v>
+        <v>954</v>
       </c>
       <c r="L5" t="n">
-        <v>860.5</v>
+        <v>919.8</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
+        <v>654</v>
+      </c>
+      <c r="C6" t="n">
+        <v>644</v>
+      </c>
+      <c r="D6" t="n">
+        <v>728</v>
+      </c>
+      <c r="E6" t="n">
+        <v>721</v>
+      </c>
+      <c r="F6" t="n">
         <v>651</v>
       </c>
-      <c r="C6" t="n">
-        <v>692</v>
-      </c>
-      <c r="D6" t="n">
-        <v>623</v>
-      </c>
-      <c r="E6" t="n">
-        <v>584</v>
-      </c>
-      <c r="F6" t="n">
-        <v>630</v>
-      </c>
       <c r="G6" t="n">
-        <v>646</v>
+        <v>766</v>
       </c>
       <c r="H6" t="n">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="I6" t="n">
-        <v>682</v>
+        <v>704</v>
       </c>
       <c r="J6" t="n">
-        <v>636</v>
+        <v>690</v>
       </c>
       <c r="K6" t="n">
-        <v>604</v>
+        <v>635</v>
       </c>
       <c r="L6" t="n">
-        <v>640.8</v>
+        <v>686.5</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>761</v>
+        <v>752</v>
       </c>
       <c r="C7" t="n">
-        <v>772</v>
+        <v>780</v>
       </c>
       <c r="D7" t="n">
-        <v>758</v>
+        <v>843</v>
       </c>
       <c r="E7" t="n">
-        <v>907</v>
+        <v>867</v>
       </c>
       <c r="F7" t="n">
-        <v>910</v>
+        <v>790</v>
       </c>
       <c r="G7" t="n">
-        <v>692</v>
+        <v>835</v>
       </c>
       <c r="H7" t="n">
-        <v>832</v>
+        <v>837</v>
       </c>
       <c r="I7" t="n">
-        <v>801</v>
+        <v>788</v>
       </c>
       <c r="J7" t="n">
-        <v>776</v>
+        <v>956</v>
       </c>
       <c r="K7" t="n">
-        <v>772</v>
+        <v>837</v>
       </c>
       <c r="L7" t="n">
-        <v>798.1</v>
+        <v>828.5</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="C8" t="n">
-        <v>656</v>
+        <v>790</v>
       </c>
       <c r="D8" t="n">
-        <v>845</v>
+        <v>710</v>
       </c>
       <c r="E8" t="n">
-        <v>730</v>
+        <v>743</v>
       </c>
       <c r="F8" t="n">
-        <v>753</v>
+        <v>643</v>
       </c>
       <c r="G8" t="n">
-        <v>641</v>
+        <v>691</v>
       </c>
       <c r="H8" t="n">
-        <v>718</v>
+        <v>736</v>
       </c>
       <c r="I8" t="n">
+        <v>731</v>
+      </c>
+      <c r="J8" t="n">
+        <v>767</v>
+      </c>
+      <c r="K8" t="n">
+        <v>615</v>
+      </c>
+      <c r="L8" t="n">
         <v>714</v>
-      </c>
-      <c r="J8" t="n">
-        <v>792</v>
-      </c>
-      <c r="K8" t="n">
-        <v>721</v>
-      </c>
-      <c r="L8" t="n">
-        <v>728.2</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>616</v>
+        <v>626</v>
       </c>
       <c r="C9" t="n">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="D9" t="n">
-        <v>673</v>
+        <v>683</v>
       </c>
       <c r="E9" t="n">
-        <v>655</v>
+        <v>688</v>
       </c>
       <c r="F9" t="n">
-        <v>675</v>
+        <v>646</v>
       </c>
       <c r="G9" t="n">
-        <v>626</v>
+        <v>705</v>
       </c>
       <c r="H9" t="n">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="I9" t="n">
-        <v>643</v>
+        <v>615</v>
       </c>
       <c r="J9" t="n">
-        <v>698</v>
+        <v>660</v>
       </c>
       <c r="K9" t="n">
-        <v>752</v>
+        <v>635</v>
       </c>
       <c r="L9" t="n">
-        <v>664.8</v>
+        <v>657</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>783</v>
+        <v>792</v>
       </c>
       <c r="C10" t="n">
-        <v>828</v>
+        <v>778</v>
       </c>
       <c r="D10" t="n">
-        <v>860</v>
+        <v>845</v>
       </c>
       <c r="E10" t="n">
-        <v>781</v>
+        <v>707</v>
       </c>
       <c r="F10" t="n">
-        <v>765</v>
+        <v>872</v>
       </c>
       <c r="G10" t="n">
-        <v>716</v>
+        <v>785</v>
       </c>
       <c r="H10" t="n">
-        <v>752</v>
+        <v>861</v>
       </c>
       <c r="I10" t="n">
-        <v>909</v>
+        <v>854</v>
       </c>
       <c r="J10" t="n">
-        <v>882</v>
+        <v>784</v>
       </c>
       <c r="K10" t="n">
-        <v>708</v>
+        <v>830</v>
       </c>
       <c r="L10" t="n">
-        <v>798.4</v>
+        <v>810.8</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>780</v>
+        <v>697</v>
       </c>
       <c r="C11" t="n">
-        <v>801</v>
+        <v>768</v>
       </c>
       <c r="D11" t="n">
-        <v>765</v>
+        <v>776</v>
       </c>
       <c r="E11" t="n">
-        <v>802</v>
+        <v>744</v>
       </c>
       <c r="F11" t="n">
-        <v>734</v>
+        <v>797</v>
       </c>
       <c r="G11" t="n">
-        <v>829</v>
+        <v>733</v>
       </c>
       <c r="H11" t="n">
-        <v>784</v>
+        <v>744</v>
       </c>
       <c r="I11" t="n">
-        <v>733</v>
+        <v>817</v>
       </c>
       <c r="J11" t="n">
-        <v>793</v>
+        <v>771</v>
       </c>
       <c r="K11" t="n">
-        <v>845</v>
+        <v>750</v>
       </c>
       <c r="L11" t="n">
-        <v>786.6</v>
+        <v>759.7</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>702</v>
+        <v>824</v>
       </c>
       <c r="C12" t="n">
-        <v>751</v>
+        <v>685</v>
       </c>
       <c r="D12" t="n">
-        <v>640</v>
+        <v>662</v>
       </c>
       <c r="E12" t="n">
-        <v>704</v>
+        <v>699</v>
       </c>
       <c r="F12" t="n">
-        <v>662</v>
+        <v>689</v>
       </c>
       <c r="G12" t="n">
-        <v>679</v>
+        <v>700</v>
       </c>
       <c r="H12" t="n">
-        <v>736</v>
+        <v>877</v>
       </c>
       <c r="I12" t="n">
-        <v>696</v>
+        <v>723</v>
       </c>
       <c r="J12" t="n">
-        <v>678</v>
+        <v>786</v>
       </c>
       <c r="K12" t="n">
-        <v>671</v>
+        <v>719</v>
       </c>
       <c r="L12" t="n">
-        <v>691.9</v>
+        <v>736.4</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>593</v>
+        <v>668</v>
       </c>
       <c r="C13" t="n">
-        <v>675</v>
+        <v>631</v>
       </c>
       <c r="D13" t="n">
-        <v>618</v>
+        <v>632</v>
       </c>
       <c r="E13" t="n">
-        <v>678</v>
+        <v>689</v>
       </c>
       <c r="F13" t="n">
-        <v>554</v>
+        <v>748</v>
       </c>
       <c r="G13" t="n">
-        <v>570</v>
+        <v>632</v>
       </c>
       <c r="H13" t="n">
-        <v>599</v>
+        <v>630</v>
       </c>
       <c r="I13" t="n">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="J13" t="n">
-        <v>595</v>
+        <v>689</v>
       </c>
       <c r="K13" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="L13" t="n">
-        <v>614.3</v>
+        <v>658.4</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>742</v>
+        <v>688</v>
       </c>
       <c r="C14" t="n">
-        <v>683</v>
+        <v>738</v>
       </c>
       <c r="D14" t="n">
-        <v>639</v>
+        <v>608</v>
       </c>
       <c r="E14" t="n">
-        <v>679</v>
+        <v>741</v>
       </c>
       <c r="F14" t="n">
-        <v>673</v>
+        <v>745</v>
       </c>
       <c r="G14" t="n">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="H14" t="n">
-        <v>560</v>
+        <v>860</v>
       </c>
       <c r="I14" t="n">
-        <v>663</v>
+        <v>677</v>
       </c>
       <c r="J14" t="n">
-        <v>636</v>
+        <v>614</v>
       </c>
       <c r="K14" t="n">
-        <v>653</v>
+        <v>743</v>
       </c>
       <c r="L14" t="n">
-        <v>653.7</v>
+        <v>703.4</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="C15" t="n">
-        <v>720</v>
+        <v>750</v>
       </c>
       <c r="D15" t="n">
-        <v>813</v>
+        <v>736</v>
       </c>
       <c r="E15" t="n">
-        <v>744</v>
+        <v>780</v>
       </c>
       <c r="F15" t="n">
-        <v>735</v>
+        <v>820</v>
       </c>
       <c r="G15" t="n">
-        <v>790</v>
+        <v>755</v>
       </c>
       <c r="H15" t="n">
+        <v>781</v>
+      </c>
+      <c r="I15" t="n">
+        <v>797</v>
+      </c>
+      <c r="J15" t="n">
         <v>736</v>
       </c>
-      <c r="I15" t="n">
-        <v>805</v>
-      </c>
-      <c r="J15" t="n">
-        <v>741</v>
-      </c>
       <c r="K15" t="n">
-        <v>748</v>
+        <v>817</v>
       </c>
       <c r="L15" t="n">
-        <v>755.7</v>
+        <v>769.3</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>724</v>
+        <v>748</v>
       </c>
       <c r="C16" t="n">
-        <v>662</v>
+        <v>727</v>
       </c>
       <c r="D16" t="n">
-        <v>712</v>
+        <v>742</v>
       </c>
       <c r="E16" t="n">
-        <v>680</v>
+        <v>699</v>
       </c>
       <c r="F16" t="n">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="G16" t="n">
-        <v>661</v>
+        <v>741</v>
       </c>
       <c r="H16" t="n">
-        <v>727</v>
+        <v>741</v>
       </c>
       <c r="I16" t="n">
-        <v>724</v>
+        <v>757</v>
       </c>
       <c r="J16" t="n">
-        <v>690</v>
+        <v>736</v>
       </c>
       <c r="K16" t="n">
-        <v>699</v>
+        <v>751</v>
       </c>
       <c r="L16" t="n">
-        <v>699.5</v>
+        <v>736</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>895</v>
+        <v>930</v>
       </c>
       <c r="C17" t="n">
-        <v>869</v>
+        <v>746</v>
       </c>
       <c r="D17" t="n">
-        <v>761</v>
+        <v>694</v>
       </c>
       <c r="E17" t="n">
-        <v>770</v>
+        <v>794</v>
       </c>
       <c r="F17" t="n">
-        <v>904</v>
+        <v>825</v>
       </c>
       <c r="G17" t="n">
-        <v>782</v>
+        <v>851</v>
       </c>
       <c r="H17" t="n">
-        <v>815</v>
+        <v>778</v>
       </c>
       <c r="I17" t="n">
-        <v>823</v>
+        <v>832</v>
       </c>
       <c r="J17" t="n">
-        <v>805</v>
+        <v>839</v>
       </c>
       <c r="K17" t="n">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="L17" t="n">
-        <v>827.6</v>
+        <v>814.4</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>667</v>
+        <v>718</v>
       </c>
       <c r="C18" t="n">
+        <v>693</v>
+      </c>
+      <c r="D18" t="n">
+        <v>700</v>
+      </c>
+      <c r="E18" t="n">
+        <v>760</v>
+      </c>
+      <c r="F18" t="n">
+        <v>680</v>
+      </c>
+      <c r="G18" t="n">
+        <v>695</v>
+      </c>
+      <c r="H18" t="n">
         <v>679</v>
       </c>
-      <c r="D18" t="n">
-        <v>683</v>
-      </c>
-      <c r="E18" t="n">
-        <v>681</v>
-      </c>
-      <c r="F18" t="n">
-        <v>655</v>
-      </c>
-      <c r="G18" t="n">
-        <v>621</v>
-      </c>
-      <c r="H18" t="n">
-        <v>691</v>
-      </c>
       <c r="I18" t="n">
-        <v>653</v>
+        <v>687</v>
       </c>
       <c r="J18" t="n">
-        <v>697</v>
+        <v>712</v>
       </c>
       <c r="K18" t="n">
-        <v>715</v>
+        <v>734</v>
       </c>
       <c r="L18" t="n">
-        <v>674.2</v>
+        <v>705.8</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>701</v>
+        <v>580</v>
       </c>
       <c r="C19" t="n">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="D19" t="n">
-        <v>669</v>
+        <v>654</v>
       </c>
       <c r="E19" t="n">
-        <v>768</v>
+        <v>590</v>
       </c>
       <c r="F19" t="n">
-        <v>689</v>
+        <v>650</v>
       </c>
       <c r="G19" t="n">
-        <v>750</v>
+        <v>657</v>
       </c>
       <c r="H19" t="n">
-        <v>686</v>
+        <v>707</v>
       </c>
       <c r="I19" t="n">
-        <v>691</v>
+        <v>645</v>
       </c>
       <c r="J19" t="n">
-        <v>692</v>
+        <v>617</v>
       </c>
       <c r="K19" t="n">
-        <v>704</v>
+        <v>670</v>
       </c>
       <c r="L19" t="n">
-        <v>700.2</v>
+        <v>641.7</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>724</v>
+        <v>641</v>
       </c>
       <c r="C20" t="n">
-        <v>699</v>
+        <v>725</v>
       </c>
       <c r="D20" t="n">
-        <v>705</v>
+        <v>688</v>
       </c>
       <c r="E20" t="n">
-        <v>695</v>
+        <v>748</v>
       </c>
       <c r="F20" t="n">
-        <v>633</v>
+        <v>753</v>
       </c>
       <c r="G20" t="n">
-        <v>742</v>
+        <v>706</v>
       </c>
       <c r="H20" t="n">
-        <v>675</v>
+        <v>752</v>
       </c>
       <c r="I20" t="n">
-        <v>796</v>
+        <v>777</v>
       </c>
       <c r="J20" t="n">
-        <v>706</v>
+        <v>722</v>
       </c>
       <c r="K20" t="n">
-        <v>641</v>
+        <v>656</v>
       </c>
       <c r="L20" t="n">
-        <v>701.6</v>
+        <v>716.8</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>703</v>
+        <v>646</v>
       </c>
       <c r="C21" t="n">
-        <v>737</v>
+        <v>664</v>
       </c>
       <c r="D21" t="n">
-        <v>714</v>
+        <v>653</v>
       </c>
       <c r="E21" t="n">
         <v>690</v>
       </c>
       <c r="F21" t="n">
-        <v>665</v>
+        <v>704</v>
       </c>
       <c r="G21" t="n">
-        <v>696</v>
+        <v>633</v>
       </c>
       <c r="H21" t="n">
-        <v>613</v>
+        <v>625</v>
       </c>
       <c r="I21" t="n">
-        <v>699</v>
+        <v>607</v>
       </c>
       <c r="J21" t="n">
-        <v>771</v>
+        <v>657</v>
       </c>
       <c r="K21" t="n">
-        <v>682</v>
+        <v>622</v>
       </c>
       <c r="L21" t="n">
-        <v>697</v>
+        <v>650.1</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
+        <v>538</v>
+      </c>
+      <c r="C22" t="n">
+        <v>639</v>
+      </c>
+      <c r="D22" t="n">
         <v>592</v>
       </c>
-      <c r="C22" t="n">
-        <v>617</v>
-      </c>
-      <c r="D22" t="n">
-        <v>558</v>
-      </c>
       <c r="E22" t="n">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="F22" t="n">
-        <v>661</v>
+        <v>530</v>
       </c>
       <c r="G22" t="n">
-        <v>636</v>
+        <v>587</v>
       </c>
       <c r="H22" t="n">
-        <v>596</v>
+        <v>508</v>
       </c>
       <c r="I22" t="n">
-        <v>600</v>
+        <v>621</v>
       </c>
       <c r="J22" t="n">
-        <v>557</v>
+        <v>652</v>
       </c>
       <c r="K22" t="n">
-        <v>634</v>
+        <v>663</v>
       </c>
       <c r="L22" t="n">
-        <v>604.6</v>
+        <v>593.2</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>676</v>
+        <v>685</v>
       </c>
       <c r="C23" t="n">
-        <v>783</v>
+        <v>760</v>
       </c>
       <c r="D23" t="n">
-        <v>694</v>
+        <v>641</v>
       </c>
       <c r="E23" t="n">
-        <v>655</v>
+        <v>729</v>
       </c>
       <c r="F23" t="n">
-        <v>674</v>
+        <v>719</v>
       </c>
       <c r="G23" t="n">
-        <v>656</v>
+        <v>706</v>
       </c>
       <c r="H23" t="n">
-        <v>673</v>
+        <v>651</v>
       </c>
       <c r="I23" t="n">
-        <v>795</v>
+        <v>724</v>
       </c>
       <c r="J23" t="n">
-        <v>733</v>
+        <v>701</v>
       </c>
       <c r="K23" t="n">
-        <v>788</v>
+        <v>745</v>
       </c>
       <c r="L23" t="n">
-        <v>712.7</v>
+        <v>706.1</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>728</v>
+        <v>683</v>
       </c>
       <c r="C24" t="n">
-        <v>710</v>
+        <v>760</v>
       </c>
       <c r="D24" t="n">
-        <v>782</v>
+        <v>670</v>
       </c>
       <c r="E24" t="n">
-        <v>859</v>
+        <v>768</v>
       </c>
       <c r="F24" t="n">
-        <v>747</v>
+        <v>660</v>
       </c>
       <c r="G24" t="n">
-        <v>742</v>
+        <v>717</v>
       </c>
       <c r="H24" t="n">
-        <v>783</v>
+        <v>678</v>
       </c>
       <c r="I24" t="n">
-        <v>722</v>
+        <v>681</v>
       </c>
       <c r="J24" t="n">
-        <v>700</v>
+        <v>676</v>
       </c>
       <c r="K24" t="n">
-        <v>769</v>
+        <v>718</v>
       </c>
       <c r="L24" t="n">
-        <v>754.2</v>
+        <v>701.1</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>722</v>
+        <v>693</v>
       </c>
       <c r="C25" t="n">
-        <v>585</v>
+        <v>649</v>
       </c>
       <c r="D25" t="n">
-        <v>687</v>
+        <v>751</v>
       </c>
       <c r="E25" t="n">
+        <v>710</v>
+      </c>
+      <c r="F25" t="n">
+        <v>663</v>
+      </c>
+      <c r="G25" t="n">
+        <v>626</v>
+      </c>
+      <c r="H25" t="n">
         <v>684</v>
       </c>
-      <c r="F25" t="n">
-        <v>671</v>
-      </c>
-      <c r="G25" t="n">
-        <v>637</v>
-      </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
+        <v>693</v>
+      </c>
+      <c r="J25" t="n">
         <v>713</v>
       </c>
-      <c r="I25" t="n">
-        <v>699</v>
-      </c>
-      <c r="J25" t="n">
-        <v>721</v>
-      </c>
       <c r="K25" t="n">
-        <v>753</v>
+        <v>694</v>
       </c>
       <c r="L25" t="n">
-        <v>687.2</v>
+        <v>687.6</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>716</v>
+        <v>785</v>
       </c>
       <c r="C26" t="n">
-        <v>814</v>
+        <v>798</v>
       </c>
       <c r="D26" t="n">
-        <v>717</v>
+        <v>820</v>
       </c>
       <c r="E26" t="n">
-        <v>758</v>
+        <v>772</v>
       </c>
       <c r="F26" t="n">
-        <v>674</v>
+        <v>783</v>
       </c>
       <c r="G26" t="n">
-        <v>673</v>
+        <v>842</v>
       </c>
       <c r="H26" t="n">
-        <v>761</v>
+        <v>795</v>
       </c>
       <c r="I26" t="n">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="J26" t="n">
-        <v>691</v>
+        <v>846</v>
       </c>
       <c r="K26" t="n">
-        <v>739</v>
+        <v>787</v>
       </c>
       <c r="L26" t="n">
-        <v>731.3</v>
+        <v>799.5</v>
       </c>
     </row>
     <row r="27">
@@ -1424,34 +1424,34 @@
         <v>885</v>
       </c>
       <c r="C27" t="n">
-        <v>815</v>
+        <v>810</v>
       </c>
       <c r="D27" t="n">
-        <v>763</v>
+        <v>732</v>
       </c>
       <c r="E27" t="n">
-        <v>877</v>
+        <v>826</v>
       </c>
       <c r="F27" t="n">
-        <v>795</v>
+        <v>758</v>
       </c>
       <c r="G27" t="n">
         <v>795</v>
       </c>
       <c r="H27" t="n">
-        <v>726</v>
+        <v>787</v>
       </c>
       <c r="I27" t="n">
-        <v>791</v>
+        <v>778</v>
       </c>
       <c r="J27" t="n">
-        <v>829</v>
+        <v>986</v>
       </c>
       <c r="K27" t="n">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="L27" t="n">
-        <v>809.1</v>
+        <v>817</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>694</v>
+        <v>653</v>
       </c>
       <c r="C28" t="n">
-        <v>652</v>
+        <v>628</v>
       </c>
       <c r="D28" t="n">
+        <v>697</v>
+      </c>
+      <c r="E28" t="n">
+        <v>692</v>
+      </c>
+      <c r="F28" t="n">
         <v>671</v>
       </c>
-      <c r="E28" t="n">
+      <c r="G28" t="n">
+        <v>640</v>
+      </c>
+      <c r="H28" t="n">
+        <v>595</v>
+      </c>
+      <c r="I28" t="n">
+        <v>657</v>
+      </c>
+      <c r="J28" t="n">
         <v>633</v>
       </c>
-      <c r="F28" t="n">
-        <v>650</v>
-      </c>
-      <c r="G28" t="n">
-        <v>580</v>
-      </c>
-      <c r="H28" t="n">
-        <v>703</v>
-      </c>
-      <c r="I28" t="n">
-        <v>606</v>
-      </c>
-      <c r="J28" t="n">
-        <v>647</v>
-      </c>
       <c r="K28" t="n">
-        <v>640</v>
+        <v>630</v>
       </c>
       <c r="L28" t="n">
-        <v>647.6</v>
+        <v>649.6</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>693</v>
+        <v>597</v>
       </c>
       <c r="C29" t="n">
-        <v>655</v>
+        <v>637</v>
       </c>
       <c r="D29" t="n">
-        <v>798</v>
+        <v>639</v>
       </c>
       <c r="E29" t="n">
-        <v>660</v>
+        <v>675</v>
       </c>
       <c r="F29" t="n">
-        <v>737</v>
+        <v>629</v>
       </c>
       <c r="G29" t="n">
-        <v>799</v>
+        <v>647</v>
       </c>
       <c r="H29" t="n">
-        <v>767</v>
+        <v>646</v>
       </c>
       <c r="I29" t="n">
-        <v>735</v>
+        <v>621</v>
       </c>
       <c r="J29" t="n">
-        <v>705</v>
+        <v>645</v>
       </c>
       <c r="K29" t="n">
-        <v>728</v>
+        <v>719</v>
       </c>
       <c r="L29" t="n">
-        <v>727.7</v>
+        <v>645.5</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>769</v>
+        <v>749</v>
       </c>
       <c r="C30" t="n">
-        <v>714</v>
+        <v>799</v>
       </c>
       <c r="D30" t="n">
-        <v>783</v>
+        <v>774</v>
       </c>
       <c r="E30" t="n">
-        <v>837</v>
+        <v>784</v>
       </c>
       <c r="F30" t="n">
-        <v>771</v>
+        <v>866</v>
       </c>
       <c r="G30" t="n">
-        <v>773</v>
+        <v>821</v>
       </c>
       <c r="H30" t="n">
-        <v>657</v>
+        <v>739</v>
       </c>
       <c r="I30" t="n">
-        <v>761</v>
+        <v>797</v>
       </c>
       <c r="J30" t="n">
-        <v>726</v>
+        <v>857</v>
       </c>
       <c r="K30" t="n">
-        <v>821</v>
+        <v>807</v>
       </c>
       <c r="L30" t="n">
-        <v>761.2</v>
+        <v>799.3</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>752</v>
+        <v>723</v>
       </c>
       <c r="C31" t="n">
-        <v>751</v>
+        <v>698</v>
       </c>
       <c r="D31" t="n">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="E31" t="n">
-        <v>746</v>
+        <v>759</v>
       </c>
       <c r="F31" t="n">
-        <v>728</v>
+        <v>764</v>
       </c>
       <c r="G31" t="n">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="H31" t="n">
-        <v>800</v>
+        <v>715</v>
       </c>
       <c r="I31" t="n">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="J31" t="n">
-        <v>678</v>
+        <v>818</v>
       </c>
       <c r="K31" t="n">
-        <v>727</v>
+        <v>697</v>
       </c>
       <c r="L31" t="n">
-        <v>737.6</v>
+        <v>736.2</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>654</v>
+        <v>728</v>
       </c>
       <c r="C32" t="n">
-        <v>678</v>
+        <v>705</v>
       </c>
       <c r="D32" t="n">
-        <v>565</v>
+        <v>634</v>
       </c>
       <c r="E32" t="n">
-        <v>672</v>
+        <v>661</v>
       </c>
       <c r="F32" t="n">
-        <v>617</v>
+        <v>701</v>
       </c>
       <c r="G32" t="n">
-        <v>702</v>
+        <v>663</v>
       </c>
       <c r="H32" t="n">
-        <v>656</v>
+        <v>669</v>
       </c>
       <c r="I32" t="n">
-        <v>571</v>
+        <v>673</v>
       </c>
       <c r="J32" t="n">
-        <v>594</v>
+        <v>578</v>
       </c>
       <c r="K32" t="n">
-        <v>629</v>
+        <v>846</v>
       </c>
       <c r="L32" t="n">
-        <v>633.8</v>
+        <v>685.8</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>788</v>
+        <v>846</v>
       </c>
       <c r="C33" t="n">
-        <v>698</v>
+        <v>772</v>
       </c>
       <c r="D33" t="n">
-        <v>693</v>
+        <v>786</v>
       </c>
       <c r="E33" t="n">
-        <v>736</v>
+        <v>804</v>
       </c>
       <c r="F33" t="n">
-        <v>770</v>
+        <v>797</v>
       </c>
       <c r="G33" t="n">
-        <v>750</v>
+        <v>803</v>
       </c>
       <c r="H33" t="n">
-        <v>700</v>
+        <v>752</v>
       </c>
       <c r="I33" t="n">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="J33" t="n">
-        <v>697</v>
+        <v>724</v>
       </c>
       <c r="K33" t="n">
-        <v>732</v>
+        <v>827</v>
       </c>
       <c r="L33" t="n">
-        <v>735.5</v>
+        <v>790.1</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>711</v>
+        <v>684</v>
       </c>
       <c r="C34" t="n">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="D34" t="n">
-        <v>638</v>
+        <v>717</v>
       </c>
       <c r="E34" t="n">
-        <v>726</v>
+        <v>673</v>
       </c>
       <c r="F34" t="n">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="G34" t="n">
-        <v>708</v>
+        <v>652</v>
       </c>
       <c r="H34" t="n">
-        <v>616</v>
+        <v>635</v>
       </c>
       <c r="I34" t="n">
-        <v>642</v>
+        <v>613</v>
       </c>
       <c r="J34" t="n">
-        <v>576</v>
+        <v>672</v>
       </c>
       <c r="K34" t="n">
-        <v>679</v>
+        <v>721</v>
       </c>
       <c r="L34" t="n">
-        <v>665.9</v>
+        <v>673.6</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>773</v>
+        <v>814</v>
       </c>
       <c r="C35" t="n">
-        <v>642</v>
+        <v>805</v>
       </c>
       <c r="D35" t="n">
-        <v>692</v>
+        <v>917</v>
       </c>
       <c r="E35" t="n">
-        <v>740</v>
+        <v>939</v>
       </c>
       <c r="F35" t="n">
-        <v>862</v>
+        <v>888</v>
       </c>
       <c r="G35" t="n">
-        <v>858</v>
+        <v>761</v>
       </c>
       <c r="H35" t="n">
-        <v>811</v>
+        <v>788</v>
       </c>
       <c r="I35" t="n">
-        <v>793</v>
+        <v>847</v>
       </c>
       <c r="J35" t="n">
-        <v>767</v>
+        <v>822</v>
       </c>
       <c r="K35" t="n">
-        <v>756</v>
+        <v>801</v>
       </c>
       <c r="L35" t="n">
-        <v>769.4</v>
+        <v>838.2</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="C36" t="n">
-        <v>689</v>
+        <v>635</v>
       </c>
       <c r="D36" t="n">
-        <v>662</v>
+        <v>624</v>
       </c>
       <c r="E36" t="n">
-        <v>580</v>
+        <v>636</v>
       </c>
       <c r="F36" t="n">
+        <v>629</v>
+      </c>
+      <c r="G36" t="n">
         <v>668</v>
       </c>
-      <c r="G36" t="n">
-        <v>623</v>
-      </c>
       <c r="H36" t="n">
-        <v>630</v>
+        <v>588</v>
       </c>
       <c r="I36" t="n">
-        <v>706</v>
+        <v>564</v>
       </c>
       <c r="J36" t="n">
-        <v>671</v>
+        <v>641</v>
       </c>
       <c r="K36" t="n">
-        <v>674</v>
+        <v>543</v>
       </c>
       <c r="L36" t="n">
-        <v>651.7</v>
+        <v>614.7</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>707</v>
+        <v>747</v>
       </c>
       <c r="C37" t="n">
-        <v>771</v>
+        <v>744</v>
       </c>
       <c r="D37" t="n">
-        <v>741</v>
+        <v>811</v>
       </c>
       <c r="E37" t="n">
-        <v>818</v>
+        <v>766</v>
       </c>
       <c r="F37" t="n">
-        <v>730</v>
+        <v>678</v>
       </c>
       <c r="G37" t="n">
-        <v>761</v>
+        <v>745</v>
       </c>
       <c r="H37" t="n">
-        <v>736</v>
+        <v>676</v>
       </c>
       <c r="I37" t="n">
-        <v>682</v>
+        <v>728</v>
       </c>
       <c r="J37" t="n">
-        <v>730</v>
+        <v>684</v>
       </c>
       <c r="K37" t="n">
-        <v>722</v>
+        <v>683</v>
       </c>
       <c r="L37" t="n">
-        <v>739.8</v>
+        <v>726.2</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>758</v>
+        <v>744</v>
       </c>
       <c r="C38" t="n">
+        <v>750</v>
+      </c>
+      <c r="D38" t="n">
+        <v>722</v>
+      </c>
+      <c r="E38" t="n">
+        <v>730</v>
+      </c>
+      <c r="F38" t="n">
+        <v>795</v>
+      </c>
+      <c r="G38" t="n">
+        <v>734</v>
+      </c>
+      <c r="H38" t="n">
+        <v>819</v>
+      </c>
+      <c r="I38" t="n">
+        <v>728</v>
+      </c>
+      <c r="J38" t="n">
+        <v>767</v>
+      </c>
+      <c r="K38" t="n">
         <v>694</v>
       </c>
-      <c r="D38" t="n">
-        <v>700</v>
-      </c>
-      <c r="E38" t="n">
-        <v>750</v>
-      </c>
-      <c r="F38" t="n">
-        <v>756</v>
-      </c>
-      <c r="G38" t="n">
-        <v>795</v>
-      </c>
-      <c r="H38" t="n">
-        <v>659</v>
-      </c>
-      <c r="I38" t="n">
-        <v>745</v>
-      </c>
-      <c r="J38" t="n">
-        <v>717</v>
-      </c>
-      <c r="K38" t="n">
-        <v>776</v>
-      </c>
       <c r="L38" t="n">
-        <v>735</v>
+        <v>748.3</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C39" t="n">
-        <v>578</v>
+        <v>552</v>
       </c>
       <c r="D39" t="n">
-        <v>594</v>
+        <v>801</v>
       </c>
       <c r="E39" t="n">
-        <v>573</v>
+        <v>542</v>
       </c>
       <c r="F39" t="n">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="G39" t="n">
-        <v>569</v>
+        <v>653</v>
       </c>
       <c r="H39" t="n">
-        <v>658</v>
+        <v>581</v>
       </c>
       <c r="I39" t="n">
-        <v>567</v>
+        <v>596</v>
       </c>
       <c r="J39" t="n">
-        <v>605</v>
+        <v>586</v>
       </c>
       <c r="K39" t="n">
-        <v>682</v>
+        <v>631</v>
       </c>
       <c r="L39" t="n">
-        <v>604.7</v>
+        <v>616.4</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>748</v>
+        <v>881</v>
       </c>
       <c r="C40" t="n">
-        <v>784</v>
+        <v>816</v>
       </c>
       <c r="D40" t="n">
-        <v>740</v>
+        <v>717</v>
       </c>
       <c r="E40" t="n">
-        <v>761</v>
+        <v>796</v>
       </c>
       <c r="F40" t="n">
-        <v>724</v>
+        <v>908</v>
       </c>
       <c r="G40" t="n">
-        <v>716</v>
+        <v>946</v>
       </c>
       <c r="H40" t="n">
-        <v>737</v>
+        <v>771</v>
       </c>
       <c r="I40" t="n">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="J40" t="n">
-        <v>748</v>
+        <v>899</v>
       </c>
       <c r="K40" t="n">
-        <v>749</v>
+        <v>709</v>
       </c>
       <c r="L40" t="n">
-        <v>752.8</v>
+        <v>826.3</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>648</v>
+        <v>630</v>
       </c>
       <c r="C41" t="n">
-        <v>734</v>
+        <v>773</v>
       </c>
       <c r="D41" t="n">
-        <v>635</v>
+        <v>597</v>
       </c>
       <c r="E41" t="n">
-        <v>744</v>
+        <v>724</v>
       </c>
       <c r="F41" t="n">
-        <v>626</v>
+        <v>681</v>
       </c>
       <c r="G41" t="n">
-        <v>711</v>
+        <v>682</v>
       </c>
       <c r="H41" t="n">
-        <v>680</v>
+        <v>625</v>
       </c>
       <c r="I41" t="n">
-        <v>600</v>
+        <v>668</v>
       </c>
       <c r="J41" t="n">
-        <v>597</v>
+        <v>615</v>
       </c>
       <c r="K41" t="n">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="L41" t="n">
-        <v>663.2</v>
+        <v>665.3</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C42" t="n">
-        <v>706</v>
+        <v>660</v>
       </c>
       <c r="D42" t="n">
-        <v>660</v>
+        <v>690</v>
       </c>
       <c r="E42" t="n">
-        <v>594</v>
+        <v>647</v>
       </c>
       <c r="F42" t="n">
-        <v>611</v>
+        <v>702</v>
       </c>
       <c r="G42" t="n">
-        <v>673</v>
+        <v>642</v>
       </c>
       <c r="H42" t="n">
-        <v>640</v>
+        <v>701</v>
       </c>
       <c r="I42" t="n">
-        <v>568</v>
+        <v>731</v>
       </c>
       <c r="J42" t="n">
-        <v>669</v>
+        <v>659</v>
       </c>
       <c r="K42" t="n">
-        <v>633</v>
+        <v>656</v>
       </c>
       <c r="L42" t="n">
-        <v>637.2</v>
+        <v>670.5</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>644</v>
+        <v>787</v>
       </c>
       <c r="C43" t="n">
-        <v>821</v>
+        <v>729</v>
       </c>
       <c r="D43" t="n">
-        <v>650</v>
+        <v>750</v>
       </c>
       <c r="E43" t="n">
-        <v>764</v>
+        <v>757</v>
       </c>
       <c r="F43" t="n">
-        <v>738</v>
+        <v>804</v>
       </c>
       <c r="G43" t="n">
-        <v>702</v>
+        <v>725</v>
       </c>
       <c r="H43" t="n">
-        <v>653</v>
+        <v>753</v>
       </c>
       <c r="I43" t="n">
-        <v>706</v>
+        <v>774</v>
       </c>
       <c r="J43" t="n">
-        <v>700</v>
+        <v>732</v>
       </c>
       <c r="K43" t="n">
-        <v>658</v>
+        <v>759</v>
       </c>
       <c r="L43" t="n">
-        <v>703.6</v>
+        <v>757</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>803</v>
+        <v>852</v>
       </c>
       <c r="C44" t="n">
-        <v>752</v>
+        <v>722</v>
       </c>
       <c r="D44" t="n">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="E44" t="n">
-        <v>769</v>
+        <v>742</v>
       </c>
       <c r="F44" t="n">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="G44" t="n">
-        <v>876</v>
+        <v>799</v>
       </c>
       <c r="H44" t="n">
-        <v>805</v>
+        <v>691</v>
       </c>
       <c r="I44" t="n">
-        <v>715</v>
+        <v>834</v>
       </c>
       <c r="J44" t="n">
-        <v>699</v>
+        <v>761</v>
       </c>
       <c r="K44" t="n">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="L44" t="n">
-        <v>772.8</v>
+        <v>770.4</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>591</v>
+        <v>606</v>
       </c>
       <c r="C45" t="n">
-        <v>628</v>
+        <v>617</v>
       </c>
       <c r="D45" t="n">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="E45" t="n">
-        <v>617</v>
+        <v>559</v>
       </c>
       <c r="F45" t="n">
-        <v>622</v>
+        <v>573</v>
       </c>
       <c r="G45" t="n">
-        <v>581</v>
+        <v>538</v>
       </c>
       <c r="H45" t="n">
-        <v>706</v>
+        <v>592</v>
       </c>
       <c r="I45" t="n">
-        <v>574</v>
+        <v>563</v>
       </c>
       <c r="J45" t="n">
-        <v>619</v>
+        <v>597</v>
       </c>
       <c r="K45" t="n">
-        <v>599</v>
+        <v>720</v>
       </c>
       <c r="L45" t="n">
-        <v>614.1</v>
+        <v>596.5</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>650</v>
+        <v>689</v>
       </c>
       <c r="C46" t="n">
-        <v>646</v>
+        <v>766</v>
       </c>
       <c r="D46" t="n">
-        <v>634</v>
+        <v>691</v>
       </c>
       <c r="E46" t="n">
-        <v>700</v>
+        <v>719</v>
       </c>
       <c r="F46" t="n">
-        <v>682</v>
+        <v>752</v>
       </c>
       <c r="G46" t="n">
-        <v>636</v>
+        <v>659</v>
       </c>
       <c r="H46" t="n">
-        <v>658</v>
+        <v>728</v>
       </c>
       <c r="I46" t="n">
-        <v>770</v>
+        <v>673</v>
       </c>
       <c r="J46" t="n">
-        <v>613</v>
+        <v>667</v>
       </c>
       <c r="K46" t="n">
-        <v>642</v>
+        <v>712</v>
       </c>
       <c r="L46" t="n">
-        <v>663.1</v>
+        <v>705.6</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>707</v>
+        <v>679</v>
       </c>
       <c r="C47" t="n">
-        <v>778</v>
+        <v>768</v>
       </c>
       <c r="D47" t="n">
-        <v>824</v>
+        <v>780</v>
       </c>
       <c r="E47" t="n">
-        <v>750</v>
+        <v>704</v>
       </c>
       <c r="F47" t="n">
-        <v>840</v>
+        <v>855</v>
       </c>
       <c r="G47" t="n">
-        <v>738</v>
+        <v>802</v>
       </c>
       <c r="H47" t="n">
-        <v>794</v>
+        <v>905</v>
       </c>
       <c r="I47" t="n">
-        <v>718</v>
+        <v>774</v>
       </c>
       <c r="J47" t="n">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="K47" t="n">
-        <v>829</v>
+        <v>849</v>
       </c>
       <c r="L47" t="n">
-        <v>776.9</v>
+        <v>791.3</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>628</v>
+        <v>768</v>
       </c>
       <c r="C48" t="n">
-        <v>704</v>
+        <v>784</v>
       </c>
       <c r="D48" t="n">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E48" t="n">
-        <v>747</v>
+        <v>777</v>
       </c>
       <c r="F48" t="n">
-        <v>722</v>
+        <v>830</v>
       </c>
       <c r="G48" t="n">
-        <v>680</v>
+        <v>821</v>
       </c>
       <c r="H48" t="n">
-        <v>641</v>
+        <v>711</v>
       </c>
       <c r="I48" t="n">
-        <v>753</v>
+        <v>832</v>
       </c>
       <c r="J48" t="n">
-        <v>709</v>
+        <v>736</v>
       </c>
       <c r="K48" t="n">
-        <v>682</v>
+        <v>755</v>
       </c>
       <c r="L48" t="n">
-        <v>699.1</v>
+        <v>773.8</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>856</v>
+        <v>814</v>
       </c>
       <c r="C49" t="n">
-        <v>886</v>
+        <v>781</v>
       </c>
       <c r="D49" t="n">
-        <v>799</v>
+        <v>783</v>
       </c>
       <c r="E49" t="n">
-        <v>790</v>
+        <v>873</v>
       </c>
       <c r="F49" t="n">
-        <v>817</v>
+        <v>846</v>
       </c>
       <c r="G49" t="n">
-        <v>796</v>
+        <v>859</v>
       </c>
       <c r="H49" t="n">
-        <v>827</v>
+        <v>838</v>
       </c>
       <c r="I49" t="n">
-        <v>774</v>
+        <v>761</v>
       </c>
       <c r="J49" t="n">
-        <v>838</v>
+        <v>768</v>
       </c>
       <c r="K49" t="n">
-        <v>860</v>
+        <v>809</v>
       </c>
       <c r="L49" t="n">
-        <v>824.3</v>
+        <v>813.2</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>607</v>
+        <v>716</v>
       </c>
       <c r="C50" t="n">
-        <v>572</v>
+        <v>766</v>
       </c>
       <c r="D50" t="n">
-        <v>672</v>
+        <v>649</v>
       </c>
       <c r="E50" t="n">
-        <v>668</v>
+        <v>742</v>
       </c>
       <c r="F50" t="n">
-        <v>751</v>
+        <v>684</v>
       </c>
       <c r="G50" t="n">
-        <v>671</v>
+        <v>682</v>
       </c>
       <c r="H50" t="n">
-        <v>634</v>
+        <v>682</v>
       </c>
       <c r="I50" t="n">
-        <v>656</v>
+        <v>678</v>
       </c>
       <c r="J50" t="n">
-        <v>777</v>
+        <v>719</v>
       </c>
       <c r="K50" t="n">
-        <v>656</v>
+        <v>713</v>
       </c>
       <c r="L50" t="n">
-        <v>666.4</v>
+        <v>703.1</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>764</v>
+        <v>690</v>
       </c>
       <c r="C51" t="n">
-        <v>710</v>
+        <v>648</v>
       </c>
       <c r="D51" t="n">
-        <v>767</v>
+        <v>711</v>
       </c>
       <c r="E51" t="n">
-        <v>699</v>
+        <v>733</v>
       </c>
       <c r="F51" t="n">
-        <v>702</v>
+        <v>739</v>
       </c>
       <c r="G51" t="n">
-        <v>698</v>
+        <v>802</v>
       </c>
       <c r="H51" t="n">
-        <v>675</v>
+        <v>708</v>
       </c>
       <c r="I51" t="n">
-        <v>598</v>
+        <v>791</v>
       </c>
       <c r="J51" t="n">
-        <v>688</v>
+        <v>717</v>
       </c>
       <c r="K51" t="n">
-        <v>755</v>
+        <v>706</v>
       </c>
       <c r="L51" t="n">
-        <v>705.6</v>
+        <v>724.5</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>710.9</v>
+        <v>716.22</v>
       </c>
       <c r="C52" t="n">
-        <v>717.42</v>
+        <v>726.74</v>
       </c>
       <c r="D52" t="n">
-        <v>710.36</v>
+        <v>720.5599999999999</v>
       </c>
       <c r="E52" t="n">
-        <v>722.5</v>
+        <v>730.34</v>
       </c>
       <c r="F52" t="n">
-        <v>714.08</v>
+        <v>736.24</v>
       </c>
       <c r="G52" t="n">
-        <v>706.28</v>
+        <v>728.28</v>
       </c>
       <c r="H52" t="n">
-        <v>705.5599999999999</v>
+        <v>723.24</v>
       </c>
       <c r="I52" t="n">
-        <v>715.84</v>
+        <v>725.64</v>
       </c>
       <c r="J52" t="n">
-        <v>708.6</v>
+        <v>730.72</v>
       </c>
       <c r="K52" t="n">
-        <v>718.4400000000001</v>
+        <v>727.8200000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>712.998</v>
+        <v>726.5799999999998</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>4.232529640197754</v>
+        <v>4.828690052032471</v>
       </c>
       <c r="C2" t="n">
-        <v>4.155235052108765</v>
+        <v>4.561888933181763</v>
       </c>
       <c r="D2" t="n">
-        <v>4.009535074234009</v>
+        <v>4.327511548995972</v>
       </c>
       <c r="E2" t="n">
-        <v>4.706926345825195</v>
+        <v>4.872106790542603</v>
       </c>
       <c r="F2" t="n">
-        <v>4.092129230499268</v>
+        <v>4.35637092590332</v>
       </c>
       <c r="G2" t="n">
-        <v>4.239576816558838</v>
+        <v>4.798535346984863</v>
       </c>
       <c r="H2" t="n">
-        <v>3.933745861053467</v>
+        <v>4.238656282424927</v>
       </c>
       <c r="I2" t="n">
-        <v>4.434120655059814</v>
+        <v>4.102229118347168</v>
       </c>
       <c r="J2" t="n">
-        <v>4.249641895294189</v>
+        <v>5.465392589569092</v>
       </c>
       <c r="K2" t="n">
-        <v>4.223548889160156</v>
+        <v>4.396422863006592</v>
       </c>
       <c r="L2" t="n">
-        <v>4.227698945999146</v>
+        <v>4.594780445098877</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>4.366650819778442</v>
+        <v>4.560650825500488</v>
       </c>
       <c r="C3" t="n">
-        <v>4.477770805358887</v>
+        <v>4.96638560295105</v>
       </c>
       <c r="D3" t="n">
-        <v>4.641014099121094</v>
+        <v>4.830716371536255</v>
       </c>
       <c r="E3" t="n">
-        <v>4.368446350097656</v>
+        <v>4.261039972305298</v>
       </c>
       <c r="F3" t="n">
-        <v>4.174712896347046</v>
+        <v>4.822815179824829</v>
       </c>
       <c r="G3" t="n">
-        <v>4.336426258087158</v>
+        <v>4.827734231948853</v>
       </c>
       <c r="H3" t="n">
-        <v>4.672909021377563</v>
+        <v>4.846694231033325</v>
       </c>
       <c r="I3" t="n">
-        <v>4.451454162597656</v>
+        <v>4.645713806152344</v>
       </c>
       <c r="J3" t="n">
-        <v>4.459892272949219</v>
+        <v>4.196812629699707</v>
       </c>
       <c r="K3" t="n">
-        <v>4.490053415298462</v>
+        <v>4.594018459320068</v>
       </c>
       <c r="L3" t="n">
-        <v>4.443933010101318</v>
+        <v>4.655258131027222</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>4.405734777450562</v>
+        <v>4.438214302062988</v>
       </c>
       <c r="C4" t="n">
-        <v>4.595498323440552</v>
+        <v>4.484579801559448</v>
       </c>
       <c r="D4" t="n">
-        <v>4.780591249465942</v>
+        <v>4.499043703079224</v>
       </c>
       <c r="E4" t="n">
-        <v>4.836331367492676</v>
+        <v>4.351929426193237</v>
       </c>
       <c r="F4" t="n">
-        <v>5.00091552734375</v>
+        <v>4.538935661315918</v>
       </c>
       <c r="G4" t="n">
-        <v>4.467727184295654</v>
+        <v>4.579375505447388</v>
       </c>
       <c r="H4" t="n">
-        <v>4.659986734390259</v>
+        <v>4.378357172012329</v>
       </c>
       <c r="I4" t="n">
-        <v>4.429621696472168</v>
+        <v>4.54344630241394</v>
       </c>
       <c r="J4" t="n">
-        <v>4.414209842681885</v>
+        <v>4.330478668212891</v>
       </c>
       <c r="K4" t="n">
-        <v>4.603530883789062</v>
+        <v>4.320941209793091</v>
       </c>
       <c r="L4" t="n">
-        <v>4.619414758682251</v>
+        <v>4.446530175209046</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>4.802260637283325</v>
+        <v>4.659659862518311</v>
       </c>
       <c r="C5" t="n">
-        <v>5.346209764480591</v>
+        <v>4.948900699615479</v>
       </c>
       <c r="D5" t="n">
-        <v>5.364202737808228</v>
+        <v>5.361865282058716</v>
       </c>
       <c r="E5" t="n">
-        <v>4.900291681289673</v>
+        <v>5.129983901977539</v>
       </c>
       <c r="F5" t="n">
-        <v>5.107866287231445</v>
+        <v>4.873600006103516</v>
       </c>
       <c r="G5" t="n">
-        <v>4.803603410720825</v>
+        <v>4.677589178085327</v>
       </c>
       <c r="H5" t="n">
-        <v>5.070129156112671</v>
+        <v>5.444443702697754</v>
       </c>
       <c r="I5" t="n">
-        <v>5.36093282699585</v>
+        <v>4.860160112380981</v>
       </c>
       <c r="J5" t="n">
-        <v>4.597599267959595</v>
+        <v>5.390848636627197</v>
       </c>
       <c r="K5" t="n">
-        <v>5.129739046096802</v>
+        <v>4.944390058517456</v>
       </c>
       <c r="L5" t="n">
-        <v>5.048283481597901</v>
+        <v>5.029144144058227</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>3.654976606369019</v>
+        <v>3.677646398544312</v>
       </c>
       <c r="C6" t="n">
-        <v>4.461293458938599</v>
+        <v>3.663516998291016</v>
       </c>
       <c r="D6" t="n">
-        <v>4.190020084381104</v>
+        <v>3.687609195709229</v>
       </c>
       <c r="E6" t="n">
-        <v>3.80888295173645</v>
+        <v>4.157732009887695</v>
       </c>
       <c r="F6" t="n">
-        <v>3.495187520980835</v>
+        <v>3.808097124099731</v>
       </c>
       <c r="G6" t="n">
-        <v>3.850901126861572</v>
+        <v>3.931802988052368</v>
       </c>
       <c r="H6" t="n">
-        <v>4.034483194351196</v>
+        <v>3.772703170776367</v>
       </c>
       <c r="I6" t="n">
-        <v>3.800016164779663</v>
+        <v>3.882338523864746</v>
       </c>
       <c r="J6" t="n">
-        <v>4.02057933807373</v>
+        <v>3.695093870162964</v>
       </c>
       <c r="K6" t="n">
-        <v>3.508943319320679</v>
+        <v>3.603825330734253</v>
       </c>
       <c r="L6" t="n">
-        <v>3.882528376579285</v>
+        <v>3.788036561012268</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>4.314293622970581</v>
+        <v>4.662665843963623</v>
       </c>
       <c r="C7" t="n">
-        <v>4.910194635391235</v>
+        <v>4.678677797317505</v>
       </c>
       <c r="D7" t="n">
-        <v>4.669088125228882</v>
+        <v>4.731201410293579</v>
       </c>
       <c r="E7" t="n">
-        <v>4.946274280548096</v>
+        <v>4.615025997161865</v>
       </c>
       <c r="F7" t="n">
-        <v>5.070524930953979</v>
+        <v>4.672011852264404</v>
       </c>
       <c r="G7" t="n">
-        <v>4.457530975341797</v>
+        <v>4.611257791519165</v>
       </c>
       <c r="H7" t="n">
-        <v>4.796015739440918</v>
+        <v>4.683581829071045</v>
       </c>
       <c r="I7" t="n">
-        <v>4.981225967407227</v>
+        <v>4.214656829833984</v>
       </c>
       <c r="J7" t="n">
-        <v>4.845164775848389</v>
+        <v>4.927680015563965</v>
       </c>
       <c r="K7" t="n">
-        <v>5.25446081161499</v>
+        <v>4.623201608657837</v>
       </c>
       <c r="L7" t="n">
-        <v>4.82447738647461</v>
+        <v>4.641996097564697</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>3.952611684799194</v>
+        <v>4.068177700042725</v>
       </c>
       <c r="C8" t="n">
-        <v>4.020389318466187</v>
+        <v>4.077079296112061</v>
       </c>
       <c r="D8" t="n">
-        <v>4.596633434295654</v>
+        <v>4.136301040649414</v>
       </c>
       <c r="E8" t="n">
-        <v>4.338915348052979</v>
+        <v>4.754022836685181</v>
       </c>
       <c r="F8" t="n">
-        <v>3.911535263061523</v>
+        <v>4.386643648147583</v>
       </c>
       <c r="G8" t="n">
-        <v>3.689816236495972</v>
+        <v>4.028967142105103</v>
       </c>
       <c r="H8" t="n">
-        <v>3.989123344421387</v>
+        <v>4.088906288146973</v>
       </c>
       <c r="I8" t="n">
-        <v>4.226432323455811</v>
+        <v>3.965694665908813</v>
       </c>
       <c r="J8" t="n">
-        <v>4.552021265029907</v>
+        <v>3.987131834030151</v>
       </c>
       <c r="K8" t="n">
-        <v>4.235089302062988</v>
+        <v>3.641680955886841</v>
       </c>
       <c r="L8" t="n">
-        <v>4.15125675201416</v>
+        <v>4.113460540771484</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>3.717021465301514</v>
+        <v>3.522538661956787</v>
       </c>
       <c r="C9" t="n">
-        <v>3.815169811248779</v>
+        <v>3.727031707763672</v>
       </c>
       <c r="D9" t="n">
-        <v>4.32324481010437</v>
+        <v>3.556938409805298</v>
       </c>
       <c r="E9" t="n">
-        <v>4.037843227386475</v>
+        <v>3.562045574188232</v>
       </c>
       <c r="F9" t="n">
-        <v>3.929727077484131</v>
+        <v>3.846618175506592</v>
       </c>
       <c r="G9" t="n">
-        <v>3.725943565368652</v>
+        <v>3.739614725112915</v>
       </c>
       <c r="H9" t="n">
-        <v>4.01941180229187</v>
+        <v>3.570225954055786</v>
       </c>
       <c r="I9" t="n">
-        <v>3.835782766342163</v>
+        <v>3.577697992324829</v>
       </c>
       <c r="J9" t="n">
-        <v>3.974439382553101</v>
+        <v>3.539321899414062</v>
       </c>
       <c r="K9" t="n">
-        <v>4.112503290176392</v>
+        <v>3.505409002304077</v>
       </c>
       <c r="L9" t="n">
-        <v>3.949108719825745</v>
+        <v>3.614744210243225</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>4.988739490509033</v>
+        <v>4.543240308761597</v>
       </c>
       <c r="C10" t="n">
-        <v>4.880865335464478</v>
+        <v>4.61703085899353</v>
       </c>
       <c r="D10" t="n">
-        <v>5.107326030731201</v>
+        <v>5.051902770996094</v>
       </c>
       <c r="E10" t="n">
-        <v>5.252108097076416</v>
+        <v>4.399557590484619</v>
       </c>
       <c r="F10" t="n">
-        <v>5.371585130691528</v>
+        <v>4.787511348724365</v>
       </c>
       <c r="G10" t="n">
-        <v>5.067906618118286</v>
+        <v>4.711255788803101</v>
       </c>
       <c r="H10" t="n">
-        <v>5.327044010162354</v>
+        <v>5.015645503997803</v>
       </c>
       <c r="I10" t="n">
-        <v>6.221319675445557</v>
+        <v>4.745433807373047</v>
       </c>
       <c r="J10" t="n">
-        <v>5.607508659362793</v>
+        <v>4.82624340057373</v>
       </c>
       <c r="K10" t="n">
-        <v>5.70667028427124</v>
+        <v>5.087023258209229</v>
       </c>
       <c r="L10" t="n">
-        <v>5.353107333183289</v>
+        <v>4.778484463691711</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>4.319382905960083</v>
+        <v>4.271442890167236</v>
       </c>
       <c r="C11" t="n">
-        <v>4.676762580871582</v>
+        <v>4.182131290435791</v>
       </c>
       <c r="D11" t="n">
-        <v>4.535073280334473</v>
+        <v>4.309298515319824</v>
       </c>
       <c r="E11" t="n">
-        <v>5.038850545883179</v>
+        <v>4.335254430770874</v>
       </c>
       <c r="F11" t="n">
-        <v>4.405003309249878</v>
+        <v>4.617718696594238</v>
       </c>
       <c r="G11" t="n">
-        <v>4.888151884078979</v>
+        <v>4.314526319503784</v>
       </c>
       <c r="H11" t="n">
-        <v>4.331136226654053</v>
+        <v>4.306878566741943</v>
       </c>
       <c r="I11" t="n">
-        <v>4.867621898651123</v>
+        <v>4.916538238525391</v>
       </c>
       <c r="J11" t="n">
-        <v>4.662405967712402</v>
+        <v>4.668417930603027</v>
       </c>
       <c r="K11" t="n">
-        <v>4.430192232131958</v>
+        <v>4.514796495437622</v>
       </c>
       <c r="L11" t="n">
-        <v>4.615458083152771</v>
+        <v>4.443700337409973</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>4.071394205093384</v>
+        <v>4.204079866409302</v>
       </c>
       <c r="C12" t="n">
-        <v>4.175811290740967</v>
+        <v>4.216082811355591</v>
       </c>
       <c r="D12" t="n">
-        <v>3.932289361953735</v>
+        <v>4.595117807388306</v>
       </c>
       <c r="E12" t="n">
-        <v>3.890028476715088</v>
+        <v>3.847610712051392</v>
       </c>
       <c r="F12" t="n">
-        <v>3.841397047042847</v>
+        <v>3.806322813034058</v>
       </c>
       <c r="G12" t="n">
-        <v>3.742966413497925</v>
+        <v>3.839891910552979</v>
       </c>
       <c r="H12" t="n">
-        <v>4.038170099258423</v>
+        <v>4.411598682403564</v>
       </c>
       <c r="I12" t="n">
-        <v>4.018027544021606</v>
+        <v>4.131274700164795</v>
       </c>
       <c r="J12" t="n">
-        <v>3.94196891784668</v>
+        <v>5.082544803619385</v>
       </c>
       <c r="K12" t="n">
-        <v>4.105626344680786</v>
+        <v>4.532258033752441</v>
       </c>
       <c r="L12" t="n">
-        <v>3.975767970085144</v>
+        <v>4.266678214073181</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>4.225420236587524</v>
+        <v>4.002756357192993</v>
       </c>
       <c r="C13" t="n">
-        <v>4.66973352432251</v>
+        <v>3.830249309539795</v>
       </c>
       <c r="D13" t="n">
-        <v>3.995363235473633</v>
+        <v>3.929873704910278</v>
       </c>
       <c r="E13" t="n">
-        <v>4.181636333465576</v>
+        <v>3.870114088058472</v>
       </c>
       <c r="F13" t="n">
-        <v>4.100944995880127</v>
+        <v>4.640174150466919</v>
       </c>
       <c r="G13" t="n">
-        <v>4.150052785873413</v>
+        <v>3.744778871536255</v>
       </c>
       <c r="H13" t="n">
-        <v>4.105421304702759</v>
+        <v>4.249073505401611</v>
       </c>
       <c r="I13" t="n">
-        <v>4.213854074478149</v>
+        <v>4.195119619369507</v>
       </c>
       <c r="J13" t="n">
-        <v>3.854986667633057</v>
+        <v>4.822550058364868</v>
       </c>
       <c r="K13" t="n">
-        <v>3.755849123001099</v>
+        <v>4.079411029815674</v>
       </c>
       <c r="L13" t="n">
-        <v>4.125326228141785</v>
+        <v>4.136410069465637</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>4.34633207321167</v>
+        <v>4.147956848144531</v>
       </c>
       <c r="C14" t="n">
-        <v>4.083541393280029</v>
+        <v>4.054447650909424</v>
       </c>
       <c r="D14" t="n">
-        <v>3.630895137786865</v>
+        <v>3.854479312896729</v>
       </c>
       <c r="E14" t="n">
-        <v>4.134293556213379</v>
+        <v>4.109846591949463</v>
       </c>
       <c r="F14" t="n">
-        <v>3.884584665298462</v>
+        <v>3.895366907119751</v>
       </c>
       <c r="G14" t="n">
-        <v>3.962726831436157</v>
+        <v>4.091180086135864</v>
       </c>
       <c r="H14" t="n">
-        <v>3.935511350631714</v>
+        <v>4.183838844299316</v>
       </c>
       <c r="I14" t="n">
-        <v>3.843614101409912</v>
+        <v>3.652210712432861</v>
       </c>
       <c r="J14" t="n">
-        <v>3.905072450637817</v>
+        <v>3.895122766494751</v>
       </c>
       <c r="K14" t="n">
-        <v>4.185808897018433</v>
+        <v>3.829264402389526</v>
       </c>
       <c r="L14" t="n">
-        <v>3.991238045692444</v>
+        <v>3.971371412277222</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>4.499492168426514</v>
+        <v>4.287596464157104</v>
       </c>
       <c r="C15" t="n">
-        <v>4.434991121292114</v>
+        <v>4.388666868209839</v>
       </c>
       <c r="D15" t="n">
-        <v>4.379424810409546</v>
+        <v>4.630232810974121</v>
       </c>
       <c r="E15" t="n">
-        <v>4.291031837463379</v>
+        <v>3.942450046539307</v>
       </c>
       <c r="F15" t="n">
-        <v>4.399301528930664</v>
+        <v>4.675640344619751</v>
       </c>
       <c r="G15" t="n">
-        <v>4.420873880386353</v>
+        <v>4.291585445404053</v>
       </c>
       <c r="H15" t="n">
-        <v>4.555498361587524</v>
+        <v>4.170994520187378</v>
       </c>
       <c r="I15" t="n">
-        <v>4.544767618179321</v>
+        <v>4.533896923065186</v>
       </c>
       <c r="J15" t="n">
-        <v>4.709469318389893</v>
+        <v>4.87911319732666</v>
       </c>
       <c r="K15" t="n">
-        <v>4.33336615562439</v>
+        <v>4.66265344619751</v>
       </c>
       <c r="L15" t="n">
-        <v>4.45682168006897</v>
+        <v>4.446283006668091</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>4.255813121795654</v>
+        <v>4.238199472427368</v>
       </c>
       <c r="C16" t="n">
-        <v>4.224159717559814</v>
+        <v>4.105056047439575</v>
       </c>
       <c r="D16" t="n">
-        <v>4.729781627655029</v>
+        <v>4.269585847854614</v>
       </c>
       <c r="E16" t="n">
-        <v>4.235677242279053</v>
+        <v>4.170876741409302</v>
       </c>
       <c r="F16" t="n">
-        <v>4.503500938415527</v>
+        <v>4.523983716964722</v>
       </c>
       <c r="G16" t="n">
-        <v>4.222731351852417</v>
+        <v>4.22689151763916</v>
       </c>
       <c r="H16" t="n">
-        <v>4.178416013717651</v>
+        <v>4.057188510894775</v>
       </c>
       <c r="I16" t="n">
-        <v>4.142143249511719</v>
+        <v>4.086092233657837</v>
       </c>
       <c r="J16" t="n">
-        <v>4.102508068084717</v>
+        <v>3.916530847549438</v>
       </c>
       <c r="K16" t="n">
-        <v>4.029959440231323</v>
+        <v>4.343447923660278</v>
       </c>
       <c r="L16" t="n">
-        <v>4.262469077110291</v>
+        <v>4.193785285949707</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>4.491215467453003</v>
+        <v>4.587686061859131</v>
       </c>
       <c r="C17" t="n">
-        <v>4.460240840911865</v>
+        <v>4.340472936630249</v>
       </c>
       <c r="D17" t="n">
-        <v>4.49994945526123</v>
+        <v>3.954939842224121</v>
       </c>
       <c r="E17" t="n">
-        <v>5.536920309066772</v>
+        <v>5.165666103363037</v>
       </c>
       <c r="F17" t="n">
-        <v>4.591663837432861</v>
+        <v>4.224508762359619</v>
       </c>
       <c r="G17" t="n">
-        <v>4.156062602996826</v>
+        <v>4.090361833572388</v>
       </c>
       <c r="H17" t="n">
-        <v>4.56846809387207</v>
+        <v>4.015580415725708</v>
       </c>
       <c r="I17" t="n">
-        <v>4.684596061706543</v>
+        <v>3.925818204879761</v>
       </c>
       <c r="J17" t="n">
-        <v>4.201424837112427</v>
+        <v>4.173644304275513</v>
       </c>
       <c r="K17" t="n">
-        <v>4.425529003143311</v>
+        <v>4.137245893478394</v>
       </c>
       <c r="L17" t="n">
-        <v>4.561607050895691</v>
+        <v>4.261592435836792</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>3.521095037460327</v>
+        <v>3.449021816253662</v>
       </c>
       <c r="C18" t="n">
-        <v>3.772810935974121</v>
+        <v>3.742824077606201</v>
       </c>
       <c r="D18" t="n">
-        <v>3.981522560119629</v>
+        <v>3.53086519241333</v>
       </c>
       <c r="E18" t="n">
-        <v>3.601254940032959</v>
+        <v>3.475143671035767</v>
       </c>
       <c r="F18" t="n">
-        <v>3.697726249694824</v>
+        <v>3.649216413497925</v>
       </c>
       <c r="G18" t="n">
-        <v>3.635642528533936</v>
+        <v>3.576111316680908</v>
       </c>
       <c r="H18" t="n">
-        <v>3.811648368835449</v>
+        <v>3.71405553817749</v>
       </c>
       <c r="I18" t="n">
-        <v>3.897339105606079</v>
+        <v>3.575945854187012</v>
       </c>
       <c r="J18" t="n">
-        <v>3.871687412261963</v>
+        <v>3.70806622505188</v>
       </c>
       <c r="K18" t="n">
-        <v>3.780128717422485</v>
+        <v>3.961937665939331</v>
       </c>
       <c r="L18" t="n">
-        <v>3.757085585594177</v>
+        <v>3.638318777084351</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>4.511646509170532</v>
+        <v>3.959405660629272</v>
       </c>
       <c r="C19" t="n">
-        <v>4.249295711517334</v>
+        <v>4.194317102432251</v>
       </c>
       <c r="D19" t="n">
-        <v>4.817636013031006</v>
+        <v>4.086127281188965</v>
       </c>
       <c r="E19" t="n">
-        <v>4.988801717758179</v>
+        <v>3.986860990524292</v>
       </c>
       <c r="F19" t="n">
-        <v>4.342148542404175</v>
+        <v>4.07261061668396</v>
       </c>
       <c r="G19" t="n">
-        <v>4.658475399017334</v>
+        <v>4.023792266845703</v>
       </c>
       <c r="H19" t="n">
-        <v>4.127384901046753</v>
+        <v>4.526973962783813</v>
       </c>
       <c r="I19" t="n">
-        <v>4.410046815872192</v>
+        <v>4.053672552108765</v>
       </c>
       <c r="J19" t="n">
-        <v>4.455266714096069</v>
+        <v>3.909530639648438</v>
       </c>
       <c r="K19" t="n">
-        <v>4.357203483581543</v>
+        <v>3.968913555145264</v>
       </c>
       <c r="L19" t="n">
-        <v>4.491790580749512</v>
+        <v>4.078220462799072</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>4.197703123092651</v>
+        <v>3.850186109542847</v>
       </c>
       <c r="C20" t="n">
-        <v>4.765138864517212</v>
+        <v>4.381528615951538</v>
       </c>
       <c r="D20" t="n">
-        <v>4.299411058425903</v>
+        <v>4.402808904647827</v>
       </c>
       <c r="E20" t="n">
-        <v>4.20158314704895</v>
+        <v>4.477638483047485</v>
       </c>
       <c r="F20" t="n">
-        <v>4.168049097061157</v>
+        <v>4.406800031661987</v>
       </c>
       <c r="G20" t="n">
-        <v>4.219139575958252</v>
+        <v>4.072656154632568</v>
       </c>
       <c r="H20" t="n">
-        <v>4.540139198303223</v>
+        <v>4.060161590576172</v>
       </c>
       <c r="I20" t="n">
-        <v>5.138089179992676</v>
+        <v>4.052677869796753</v>
       </c>
       <c r="J20" t="n">
-        <v>4.201306104660034</v>
+        <v>3.910553932189941</v>
       </c>
       <c r="K20" t="n">
-        <v>4.699037313461304</v>
+        <v>3.966915845870972</v>
       </c>
       <c r="L20" t="n">
-        <v>4.442959666252136</v>
+        <v>4.158192753791809</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>4.218425273895264</v>
+        <v>4.073154449462891</v>
       </c>
       <c r="C21" t="n">
-        <v>4.82206916809082</v>
+        <v>4.002803802490234</v>
       </c>
       <c r="D21" t="n">
-        <v>4.4710853099823</v>
+        <v>4.080591917037964</v>
       </c>
       <c r="E21" t="n">
-        <v>4.527851581573486</v>
+        <v>4.247682571411133</v>
       </c>
       <c r="F21" t="n">
-        <v>4.430464029312134</v>
+        <v>3.88409161567688</v>
       </c>
       <c r="G21" t="n">
-        <v>4.474086046218872</v>
+        <v>4.079139709472656</v>
       </c>
       <c r="H21" t="n">
-        <v>4.118080139160156</v>
+        <v>4.073145151138306</v>
       </c>
       <c r="I21" t="n">
-        <v>4.294469356536865</v>
+        <v>4.113322973251343</v>
       </c>
       <c r="J21" t="n">
-        <v>4.517942667007446</v>
+        <v>3.794136524200439</v>
       </c>
       <c r="K21" t="n">
-        <v>4.67719841003418</v>
+        <v>4.126754999160767</v>
       </c>
       <c r="L21" t="n">
-        <v>4.455167198181153</v>
+        <v>4.047482371330261</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>4.11874532699585</v>
+        <v>3.898409366607666</v>
       </c>
       <c r="C22" t="n">
-        <v>4.190639972686768</v>
+        <v>4.058463335037231</v>
       </c>
       <c r="D22" t="n">
-        <v>4.156065702438354</v>
+        <v>4.082365751266479</v>
       </c>
       <c r="E22" t="n">
-        <v>4.049652814865112</v>
+        <v>3.899311542510986</v>
       </c>
       <c r="F22" t="n">
-        <v>4.214757680892944</v>
+        <v>3.999614953994751</v>
       </c>
       <c r="G22" t="n">
-        <v>4.233583211898804</v>
+        <v>4.253615140914917</v>
       </c>
       <c r="H22" t="n">
-        <v>4.120646476745605</v>
+        <v>3.914330720901489</v>
       </c>
       <c r="I22" t="n">
-        <v>4.360792636871338</v>
+        <v>4.020754337310791</v>
       </c>
       <c r="J22" t="n">
-        <v>4.453175783157349</v>
+        <v>4.052186250686646</v>
       </c>
       <c r="K22" t="n">
-        <v>4.263364553451538</v>
+        <v>4.144931793212891</v>
       </c>
       <c r="L22" t="n">
-        <v>4.216142416000366</v>
+        <v>4.032398319244384</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>4.05836296081543</v>
+        <v>4.105739593505859</v>
       </c>
       <c r="C23" t="n">
-        <v>4.13206934928894</v>
+        <v>4.332269430160522</v>
       </c>
       <c r="D23" t="n">
-        <v>4.085978031158447</v>
+        <v>4.168172597885132</v>
       </c>
       <c r="E23" t="n">
-        <v>4.523505210876465</v>
+        <v>4.276398420333862</v>
       </c>
       <c r="F23" t="n">
-        <v>4.030524730682373</v>
+        <v>4.164107322692871</v>
       </c>
       <c r="G23" t="n">
-        <v>4.182750701904297</v>
+        <v>3.893423318862915</v>
       </c>
       <c r="H23" t="n">
-        <v>4.191240787506104</v>
+        <v>4.028529405593872</v>
       </c>
       <c r="I23" t="n">
-        <v>4.138918161392212</v>
+        <v>3.829038143157959</v>
       </c>
       <c r="J23" t="n">
-        <v>4.192108869552612</v>
+        <v>3.915487051010132</v>
       </c>
       <c r="K23" t="n">
-        <v>4.616653919219971</v>
+        <v>4.067634105682373</v>
       </c>
       <c r="L23" t="n">
-        <v>4.215211272239685</v>
+        <v>4.07807993888855</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>4.178068161010742</v>
+        <v>3.812333583831787</v>
       </c>
       <c r="C24" t="n">
-        <v>4.204626321792603</v>
+        <v>3.783368825912476</v>
       </c>
       <c r="D24" t="n">
-        <v>4.255957365036011</v>
+        <v>3.999932289123535</v>
       </c>
       <c r="E24" t="n">
-        <v>4.416884183883667</v>
+        <v>4.080581188201904</v>
       </c>
       <c r="F24" t="n">
-        <v>4.124558687210083</v>
+        <v>3.765931606292725</v>
       </c>
       <c r="G24" t="n">
-        <v>4.076325654983521</v>
+        <v>4.346997499465942</v>
       </c>
       <c r="H24" t="n">
-        <v>4.159946203231812</v>
+        <v>3.700560569763184</v>
       </c>
       <c r="I24" t="n">
-        <v>4.401018381118774</v>
+        <v>4.060677289962769</v>
       </c>
       <c r="J24" t="n">
-        <v>4.21812891960144</v>
+        <v>4.258697271347046</v>
       </c>
       <c r="K24" t="n">
-        <v>4.531930923461914</v>
+        <v>4.011789083480835</v>
       </c>
       <c r="L24" t="n">
-        <v>4.256744480133056</v>
+        <v>3.98208692073822</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>3.885921478271484</v>
+        <v>3.674649953842163</v>
       </c>
       <c r="C25" t="n">
-        <v>3.558413743972778</v>
+        <v>3.618105411529541</v>
       </c>
       <c r="D25" t="n">
-        <v>3.788381576538086</v>
+        <v>5.529975414276123</v>
       </c>
       <c r="E25" t="n">
-        <v>3.728133201599121</v>
+        <v>8.454764366149902</v>
       </c>
       <c r="F25" t="n">
-        <v>3.564244270324707</v>
+        <v>3.714076280593872</v>
       </c>
       <c r="G25" t="n">
-        <v>3.728147983551025</v>
+        <v>3.623780965805054</v>
       </c>
       <c r="H25" t="n">
-        <v>3.805827617645264</v>
+        <v>3.73102855682373</v>
       </c>
       <c r="I25" t="n">
-        <v>4.045420408248901</v>
+        <v>3.516059875488281</v>
       </c>
       <c r="J25" t="n">
-        <v>4.113036632537842</v>
+        <v>4.175665616989136</v>
       </c>
       <c r="K25" t="n">
-        <v>3.804961442947388</v>
+        <v>3.750211715698242</v>
       </c>
       <c r="L25" t="n">
-        <v>3.80224883556366</v>
+        <v>4.378831815719605</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>4.360168695449829</v>
+        <v>4.686089992523193</v>
       </c>
       <c r="C26" t="n">
-        <v>4.52236008644104</v>
+        <v>4.294569253921509</v>
       </c>
       <c r="D26" t="n">
-        <v>4.807947874069214</v>
+        <v>4.500524282455444</v>
       </c>
       <c r="E26" t="n">
-        <v>4.379603624343872</v>
+        <v>4.45816445350647</v>
       </c>
       <c r="F26" t="n">
-        <v>4.358060598373413</v>
+        <v>4.285526275634766</v>
       </c>
       <c r="G26" t="n">
-        <v>4.243790864944458</v>
+        <v>4.270440578460693</v>
       </c>
       <c r="H26" t="n">
-        <v>4.261706113815308</v>
+        <v>4.543694257736206</v>
       </c>
       <c r="I26" t="n">
-        <v>4.716282844543457</v>
+        <v>4.286481618881226</v>
       </c>
       <c r="J26" t="n">
-        <v>4.370042562484741</v>
+        <v>4.810771226882935</v>
       </c>
       <c r="K26" t="n">
-        <v>4.470637559890747</v>
+        <v>4.167396068572998</v>
       </c>
       <c r="L26" t="n">
-        <v>4.449060082435608</v>
+        <v>4.430365800857544</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>5.16685938835144</v>
+        <v>4.583835363388062</v>
       </c>
       <c r="C27" t="n">
-        <v>4.886940956115723</v>
+        <v>4.581235408782959</v>
       </c>
       <c r="D27" t="n">
-        <v>4.534543752670288</v>
+        <v>4.672382354736328</v>
       </c>
       <c r="E27" t="n">
-        <v>4.65649151802063</v>
+        <v>4.8065505027771</v>
       </c>
       <c r="F27" t="n">
-        <v>5.055029153823853</v>
+        <v>4.407563447952271</v>
       </c>
       <c r="G27" t="n">
-        <v>5.248226404190063</v>
+        <v>4.415528774261475</v>
       </c>
       <c r="H27" t="n">
-        <v>4.425766468048096</v>
+        <v>4.392572402954102</v>
       </c>
       <c r="I27" t="n">
-        <v>4.98889422416687</v>
+        <v>4.390081405639648</v>
       </c>
       <c r="J27" t="n">
-        <v>4.693298816680908</v>
+        <v>4.90175986289978</v>
       </c>
       <c r="K27" t="n">
-        <v>4.700098752975464</v>
+        <v>4.372763633728027</v>
       </c>
       <c r="L27" t="n">
-        <v>4.835614943504334</v>
+        <v>4.552427315711975</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>4.166298866271973</v>
+        <v>3.824056386947632</v>
       </c>
       <c r="C28" t="n">
-        <v>4.082360506057739</v>
+        <v>3.950742244720459</v>
       </c>
       <c r="D28" t="n">
-        <v>4.301582098007202</v>
+        <v>4.137979984283447</v>
       </c>
       <c r="E28" t="n">
-        <v>4.017607927322388</v>
+        <v>4.114035129547119</v>
       </c>
       <c r="F28" t="n">
-        <v>4.288185596466064</v>
+        <v>4.004806756973267</v>
       </c>
       <c r="G28" t="n">
-        <v>4.061845779418945</v>
+        <v>3.849187850952148</v>
       </c>
       <c r="H28" t="n">
-        <v>4.235242605209351</v>
+        <v>3.833745956420898</v>
       </c>
       <c r="I28" t="n">
-        <v>4.134915828704834</v>
+        <v>4.223278760910034</v>
       </c>
       <c r="J28" t="n">
-        <v>4.146557569503784</v>
+        <v>3.89760160446167</v>
       </c>
       <c r="K28" t="n">
-        <v>4.225879430770874</v>
+        <v>4.14598822593689</v>
       </c>
       <c r="L28" t="n">
-        <v>4.166047620773315</v>
+        <v>3.998142290115356</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>4.43401050567627</v>
+        <v>3.699074745178223</v>
       </c>
       <c r="C29" t="n">
-        <v>4.158187627792358</v>
+        <v>3.732990026473999</v>
       </c>
       <c r="D29" t="n">
-        <v>4.681694507598877</v>
+        <v>3.875619888305664</v>
       </c>
       <c r="E29" t="n">
-        <v>4.045112609863281</v>
+        <v>3.929505586624146</v>
       </c>
       <c r="F29" t="n">
-        <v>4.249866962432861</v>
+        <v>3.765411376953125</v>
       </c>
       <c r="G29" t="n">
-        <v>4.531995534896851</v>
+        <v>3.848186731338501</v>
       </c>
       <c r="H29" t="n">
-        <v>4.859251022338867</v>
+        <v>3.717036485671997</v>
       </c>
       <c r="I29" t="n">
-        <v>4.118021965026855</v>
+        <v>3.773400783538818</v>
       </c>
       <c r="J29" t="n">
-        <v>4.283459901809692</v>
+        <v>4.123001575469971</v>
       </c>
       <c r="K29" t="n">
-        <v>4.183501482009888</v>
+        <v>4.081099271774292</v>
       </c>
       <c r="L29" t="n">
-        <v>4.35451021194458</v>
+        <v>3.854532647132873</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>4.184800386428833</v>
+        <v>4.015565633773804</v>
       </c>
       <c r="C30" t="n">
-        <v>4.150761365890503</v>
+        <v>4.403587102890015</v>
       </c>
       <c r="D30" t="n">
-        <v>4.700497150421143</v>
+        <v>4.893321752548218</v>
       </c>
       <c r="E30" t="n">
-        <v>4.860712766647339</v>
+        <v>4.530103921890259</v>
       </c>
       <c r="F30" t="n">
-        <v>4.653208494186401</v>
+        <v>4.426736831665039</v>
       </c>
       <c r="G30" t="n">
-        <v>4.765090942382812</v>
+        <v>4.051930904388428</v>
       </c>
       <c r="H30" t="n">
-        <v>4.172435760498047</v>
+        <v>4.334747076034546</v>
       </c>
       <c r="I30" t="n">
-        <v>4.602373361587524</v>
+        <v>4.426106929779053</v>
       </c>
       <c r="J30" t="n">
-        <v>4.28634238243103</v>
+        <v>4.259006023406982</v>
       </c>
       <c r="K30" t="n">
-        <v>4.511220455169678</v>
+        <v>4.786569118499756</v>
       </c>
       <c r="L30" t="n">
-        <v>4.488744306564331</v>
+        <v>4.41276752948761</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>3.924669742584229</v>
+        <v>3.736782073974609</v>
       </c>
       <c r="C31" t="n">
-        <v>4.126458644866943</v>
+        <v>3.790137767791748</v>
       </c>
       <c r="D31" t="n">
-        <v>4.057969093322754</v>
+        <v>3.878420114517212</v>
       </c>
       <c r="E31" t="n">
-        <v>3.872719764709473</v>
+        <v>3.845122337341309</v>
       </c>
       <c r="F31" t="n">
-        <v>4.063116550445557</v>
+        <v>3.952904224395752</v>
       </c>
       <c r="G31" t="n">
-        <v>3.884749412536621</v>
+        <v>4.043232202529907</v>
       </c>
       <c r="H31" t="n">
-        <v>4.067998647689819</v>
+        <v>4.20134425163269</v>
       </c>
       <c r="I31" t="n">
-        <v>3.976435422897339</v>
+        <v>4.430765628814697</v>
       </c>
       <c r="J31" t="n">
-        <v>3.934020519256592</v>
+        <v>4.613341569900513</v>
       </c>
       <c r="K31" t="n">
-        <v>3.998449802398682</v>
+        <v>4.111069202423096</v>
       </c>
       <c r="L31" t="n">
-        <v>3.990658760070801</v>
+        <v>4.060311937332154</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>3.906765937805176</v>
+        <v>4.359419345855713</v>
       </c>
       <c r="C32" t="n">
-        <v>4.218865633010864</v>
+        <v>3.831745624542236</v>
       </c>
       <c r="D32" t="n">
-        <v>3.854687452316284</v>
+        <v>4.047679662704468</v>
       </c>
       <c r="E32" t="n">
-        <v>4.00307559967041</v>
+        <v>3.93848729133606</v>
       </c>
       <c r="F32" t="n">
-        <v>4.265479326248169</v>
+        <v>4.167377710342407</v>
       </c>
       <c r="G32" t="n">
-        <v>3.987102270126343</v>
+        <v>4.36986517906189</v>
       </c>
       <c r="H32" t="n">
-        <v>4.138942003250122</v>
+        <v>3.98435640335083</v>
       </c>
       <c r="I32" t="n">
-        <v>3.808991193771362</v>
+        <v>4.148437976837158</v>
       </c>
       <c r="J32" t="n">
-        <v>3.860962390899658</v>
+        <v>3.910542964935303</v>
       </c>
       <c r="K32" t="n">
-        <v>4.150595426559448</v>
+        <v>4.93291449546814</v>
       </c>
       <c r="L32" t="n">
-        <v>4.019546723365783</v>
+        <v>4.169082665443421</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>4.226166248321533</v>
+        <v>4.891083955764771</v>
       </c>
       <c r="C33" t="n">
-        <v>4.380578279495239</v>
+        <v>4.747400283813477</v>
       </c>
       <c r="D33" t="n">
-        <v>4.265994787216187</v>
+        <v>4.389808177947998</v>
       </c>
       <c r="E33" t="n">
-        <v>4.459844350814819</v>
+        <v>4.729444026947021</v>
       </c>
       <c r="F33" t="n">
-        <v>4.240965366363525</v>
+        <v>4.773764133453369</v>
       </c>
       <c r="G33" t="n">
-        <v>4.181539535522461</v>
+        <v>4.384612083435059</v>
       </c>
       <c r="H33" t="n">
-        <v>4.645396709442139</v>
+        <v>4.422477960586548</v>
       </c>
       <c r="I33" t="n">
-        <v>4.135588884353638</v>
+        <v>4.798532247543335</v>
       </c>
       <c r="J33" t="n">
-        <v>4.101532936096191</v>
+        <v>4.549698352813721</v>
       </c>
       <c r="K33" t="n">
-        <v>4.425832509994507</v>
+        <v>4.530726194381714</v>
       </c>
       <c r="L33" t="n">
-        <v>4.306343960762024</v>
+        <v>4.621754741668701</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>3.778690099716187</v>
+        <v>3.945740222930908</v>
       </c>
       <c r="C34" t="n">
-        <v>3.893723249435425</v>
+        <v>3.866924524307251</v>
       </c>
       <c r="D34" t="n">
-        <v>3.899870872497559</v>
+        <v>4.006583213806152</v>
       </c>
       <c r="E34" t="n">
-        <v>3.848015546798706</v>
+        <v>3.858469724655151</v>
       </c>
       <c r="F34" t="n">
-        <v>3.861783981323242</v>
+        <v>4.010582685470581</v>
       </c>
       <c r="G34" t="n">
-        <v>3.702673435211182</v>
+        <v>3.976159334182739</v>
       </c>
       <c r="H34" t="n">
-        <v>4.062767744064331</v>
+        <v>3.868418455123901</v>
       </c>
       <c r="I34" t="n">
-        <v>4.067398548126221</v>
+        <v>3.872428417205811</v>
       </c>
       <c r="J34" t="n">
-        <v>3.679862022399902</v>
+        <v>4.02851676940918</v>
       </c>
       <c r="K34" t="n">
-        <v>3.977750062942505</v>
+        <v>3.809074878692627</v>
       </c>
       <c r="L34" t="n">
-        <v>3.877253556251526</v>
+        <v>3.92428982257843</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>4.719942331314087</v>
+        <v>4.877812385559082</v>
       </c>
       <c r="C35" t="n">
-        <v>4.549704074859619</v>
+        <v>4.649885177612305</v>
       </c>
       <c r="D35" t="n">
-        <v>4.672670602798462</v>
+        <v>5.367043018341064</v>
       </c>
       <c r="E35" t="n">
-        <v>4.790496349334717</v>
+        <v>5.227397918701172</v>
       </c>
       <c r="F35" t="n">
-        <v>4.873196363449097</v>
+        <v>5.262301445007324</v>
       </c>
       <c r="G35" t="n">
-        <v>5.80324387550354</v>
+        <v>4.744629144668579</v>
       </c>
       <c r="H35" t="n">
-        <v>4.525646686553955</v>
+        <v>5.131160020828247</v>
       </c>
       <c r="I35" t="n">
-        <v>4.687664270401001</v>
+        <v>4.909728527069092</v>
       </c>
       <c r="J35" t="n">
-        <v>4.879510879516602</v>
+        <v>5.011530160903931</v>
       </c>
       <c r="K35" t="n">
-        <v>5.148670673370361</v>
+        <v>4.805744171142578</v>
       </c>
       <c r="L35" t="n">
-        <v>4.865074610710144</v>
+        <v>4.998723196983337</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>3.620358467102051</v>
+        <v>3.468672275543213</v>
       </c>
       <c r="C36" t="n">
-        <v>3.429636001586914</v>
+        <v>3.493094444274902</v>
       </c>
       <c r="D36" t="n">
-        <v>3.640225172042847</v>
+        <v>3.38536810874939</v>
       </c>
       <c r="E36" t="n">
-        <v>3.698319673538208</v>
+        <v>3.500575065612793</v>
       </c>
       <c r="F36" t="n">
-        <v>3.519641399383545</v>
+        <v>3.54247260093689</v>
       </c>
       <c r="G36" t="n">
-        <v>3.660724639892578</v>
+        <v>3.636278390884399</v>
       </c>
       <c r="H36" t="n">
-        <v>3.528290033340454</v>
+        <v>3.64669942855835</v>
       </c>
       <c r="I36" t="n">
-        <v>3.509446144104004</v>
+        <v>3.602832555770874</v>
       </c>
       <c r="J36" t="n">
-        <v>3.732579231262207</v>
+        <v>3.464669466018677</v>
       </c>
       <c r="K36" t="n">
-        <v>3.530755043029785</v>
+        <v>3.539470672607422</v>
       </c>
       <c r="L36" t="n">
-        <v>3.586997580528259</v>
+        <v>3.528013300895691</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>4.322865009307861</v>
+        <v>4.346429824829102</v>
       </c>
       <c r="C37" t="n">
-        <v>4.447990894317627</v>
+        <v>4.507761001586914</v>
       </c>
       <c r="D37" t="n">
-        <v>4.370468139648438</v>
+        <v>4.887798547744751</v>
       </c>
       <c r="E37" t="n">
-        <v>4.651795864105225</v>
+        <v>4.331232786178589</v>
       </c>
       <c r="F37" t="n">
-        <v>4.36440634727478</v>
+        <v>4.495805025100708</v>
       </c>
       <c r="G37" t="n">
-        <v>4.327968597412109</v>
+        <v>4.469862461090088</v>
       </c>
       <c r="H37" t="n">
-        <v>4.641194105148315</v>
+        <v>4.400557994842529</v>
       </c>
       <c r="I37" t="n">
-        <v>4.145598411560059</v>
+        <v>4.890825986862183</v>
       </c>
       <c r="J37" t="n">
-        <v>4.293562889099121</v>
+        <v>4.825325727462769</v>
       </c>
       <c r="K37" t="n">
-        <v>4.085322856903076</v>
+        <v>4.662900924682617</v>
       </c>
       <c r="L37" t="n">
-        <v>4.365117311477661</v>
+        <v>4.581850028038025</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>4.731975555419922</v>
+        <v>4.427986621856689</v>
       </c>
       <c r="C38" t="n">
-        <v>4.293674468994141</v>
+        <v>4.702782869338989</v>
       </c>
       <c r="D38" t="n">
-        <v>4.331881761550903</v>
+        <v>5.803961277008057</v>
       </c>
       <c r="E38" t="n">
-        <v>4.390513896942139</v>
+        <v>4.232534170150757</v>
       </c>
       <c r="F38" t="n">
-        <v>4.731743335723877</v>
+        <v>4.578611373901367</v>
       </c>
       <c r="G38" t="n">
-        <v>4.213690757751465</v>
+        <v>4.873892545700073</v>
       </c>
       <c r="H38" t="n">
-        <v>4.242744922637939</v>
+        <v>4.795560598373413</v>
       </c>
       <c r="I38" t="n">
-        <v>4.314799547195435</v>
+        <v>4.25193452835083</v>
       </c>
       <c r="J38" t="n">
-        <v>4.192287921905518</v>
+        <v>4.495031595230103</v>
       </c>
       <c r="K38" t="n">
-        <v>4.794023990631104</v>
+        <v>4.193431615829468</v>
       </c>
       <c r="L38" t="n">
-        <v>4.423733615875244</v>
+        <v>4.635572719573974</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>3.982802391052246</v>
+        <v>4.546998977661133</v>
       </c>
       <c r="C39" t="n">
-        <v>3.657760381698608</v>
+        <v>5.034828662872314</v>
       </c>
       <c r="D39" t="n">
-        <v>3.952635288238525</v>
+        <v>4.530986547470093</v>
       </c>
       <c r="E39" t="n">
-        <v>3.796126842498779</v>
+        <v>3.905576229095459</v>
       </c>
       <c r="F39" t="n">
-        <v>4.030844449996948</v>
+        <v>4.012861251831055</v>
       </c>
       <c r="G39" t="n">
-        <v>3.839843034744263</v>
+        <v>4.010812044143677</v>
       </c>
       <c r="H39" t="n">
-        <v>3.972718000411987</v>
+        <v>3.916538238525391</v>
       </c>
       <c r="I39" t="n">
-        <v>3.765441179275513</v>
+        <v>3.939498901367188</v>
       </c>
       <c r="J39" t="n">
-        <v>3.888749361038208</v>
+        <v>3.822292327880859</v>
       </c>
       <c r="K39" t="n">
-        <v>3.857672929763794</v>
+        <v>4.071149110794067</v>
       </c>
       <c r="L39" t="n">
-        <v>3.874459385871887</v>
+        <v>4.179154229164124</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>4.528051853179932</v>
+        <v>5.017283201217651</v>
       </c>
       <c r="C40" t="n">
-        <v>4.536803722381592</v>
+        <v>4.691062211990356</v>
       </c>
       <c r="D40" t="n">
-        <v>4.311723232269287</v>
+        <v>4.978388786315918</v>
       </c>
       <c r="E40" t="n">
-        <v>4.607755661010742</v>
+        <v>5.004321336746216</v>
       </c>
       <c r="F40" t="n">
-        <v>4.309170246124268</v>
+        <v>4.582388639450073</v>
       </c>
       <c r="G40" t="n">
-        <v>4.42572021484375</v>
+        <v>4.853675365447998</v>
       </c>
       <c r="H40" t="n">
-        <v>4.280476808547974</v>
+        <v>6.299703121185303</v>
       </c>
       <c r="I40" t="n">
-        <v>4.661551952362061</v>
+        <v>6.700627326965332</v>
       </c>
       <c r="J40" t="n">
-        <v>4.184892177581787</v>
+        <v>6.425767421722412</v>
       </c>
       <c r="K40" t="n">
-        <v>4.275488615036011</v>
+        <v>4.654168605804443</v>
       </c>
       <c r="L40" t="n">
-        <v>4.41216344833374</v>
+        <v>5.32073860168457</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>4.247084379196167</v>
+        <v>4.92405366897583</v>
       </c>
       <c r="C41" t="n">
-        <v>4.420494079589844</v>
+        <v>4.741478443145752</v>
       </c>
       <c r="D41" t="n">
-        <v>4.236037969589233</v>
+        <v>4.352987766265869</v>
       </c>
       <c r="E41" t="n">
-        <v>4.911481380462646</v>
+        <v>6.283161878585815</v>
       </c>
       <c r="F41" t="n">
-        <v>4.188785076141357</v>
+        <v>5.996895790100098</v>
       </c>
       <c r="G41" t="n">
-        <v>4.185672998428345</v>
+        <v>4.962909698486328</v>
       </c>
       <c r="H41" t="n">
-        <v>4.293381690979004</v>
+        <v>4.489602565765381</v>
       </c>
       <c r="I41" t="n">
-        <v>4.273151159286499</v>
+        <v>4.437252759933472</v>
       </c>
       <c r="J41" t="n">
-        <v>4.242496252059937</v>
+        <v>5.402426481246948</v>
       </c>
       <c r="K41" t="n">
-        <v>4.420774459838867</v>
+        <v>6.033876895904541</v>
       </c>
       <c r="L41" t="n">
-        <v>4.34193594455719</v>
+        <v>5.162464594841003</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>4.156673192977905</v>
+        <v>4.590401411056519</v>
       </c>
       <c r="C42" t="n">
-        <v>4.700155973434448</v>
+        <v>5.808343648910522</v>
       </c>
       <c r="D42" t="n">
-        <v>4.423436641693115</v>
+        <v>4.96195125579834</v>
       </c>
       <c r="E42" t="n">
-        <v>3.993559837341309</v>
+        <v>4.136529207229614</v>
       </c>
       <c r="F42" t="n">
-        <v>4.326821565628052</v>
+        <v>4.215313673019409</v>
       </c>
       <c r="G42" t="n">
-        <v>4.092047214508057</v>
+        <v>4.303567409515381</v>
       </c>
       <c r="H42" t="n">
-        <v>4.277757406234741</v>
+        <v>4.314517974853516</v>
       </c>
       <c r="I42" t="n">
-        <v>4.340255737304688</v>
+        <v>4.598282098770142</v>
       </c>
       <c r="J42" t="n">
-        <v>4.33000659942627</v>
+        <v>4.463991165161133</v>
       </c>
       <c r="K42" t="n">
-        <v>4.306123971939087</v>
+        <v>4.514024257659912</v>
       </c>
       <c r="L42" t="n">
-        <v>4.294683814048767</v>
+        <v>4.590692210197449</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>4.552305698394775</v>
+        <v>4.623068809509277</v>
       </c>
       <c r="C43" t="n">
-        <v>5.038972616195679</v>
+        <v>4.71424126625061</v>
       </c>
       <c r="D43" t="n">
-        <v>4.124902009963989</v>
+        <v>4.588078737258911</v>
       </c>
       <c r="E43" t="n">
-        <v>4.248546600341797</v>
+        <v>4.918813943862915</v>
       </c>
       <c r="F43" t="n">
-        <v>4.373288869857788</v>
+        <v>5.228411197662354</v>
       </c>
       <c r="G43" t="n">
-        <v>4.423182964324951</v>
+        <v>5.270389318466187</v>
       </c>
       <c r="H43" t="n">
-        <v>4.627526998519897</v>
+        <v>5.157619476318359</v>
       </c>
       <c r="I43" t="n">
-        <v>4.544088363647461</v>
+        <v>5.02805757522583</v>
       </c>
       <c r="J43" t="n">
-        <v>4.590970277786255</v>
+        <v>5.867788314819336</v>
       </c>
       <c r="K43" t="n">
-        <v>4.349853277206421</v>
+        <v>4.564262866973877</v>
       </c>
       <c r="L43" t="n">
-        <v>4.487363767623902</v>
+        <v>4.996073150634766</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>4.377628803253174</v>
+        <v>3.914983749389648</v>
       </c>
       <c r="C44" t="n">
-        <v>3.93687629699707</v>
+        <v>3.821937561035156</v>
       </c>
       <c r="D44" t="n">
-        <v>4.169073581695557</v>
+        <v>3.959943056106567</v>
       </c>
       <c r="E44" t="n">
-        <v>4.274339914321899</v>
+        <v>4.159541368484497</v>
       </c>
       <c r="F44" t="n">
-        <v>4.430176258087158</v>
+        <v>3.762230157852173</v>
       </c>
       <c r="G44" t="n">
-        <v>4.356356143951416</v>
+        <v>3.880899906158447</v>
       </c>
       <c r="H44" t="n">
-        <v>4.122358560562134</v>
+        <v>4.075920104980469</v>
       </c>
       <c r="I44" t="n">
-        <v>3.886156797409058</v>
+        <v>4.042511224746704</v>
       </c>
       <c r="J44" t="n">
-        <v>3.979609251022339</v>
+        <v>3.811079740524292</v>
       </c>
       <c r="K44" t="n">
-        <v>4.050922155380249</v>
+        <v>4.13924765586853</v>
       </c>
       <c r="L44" t="n">
-        <v>4.158349776268006</v>
+        <v>3.956829452514648</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>4.06973123550415</v>
+        <v>3.783657312393188</v>
       </c>
       <c r="C45" t="n">
-        <v>4.14562726020813</v>
+        <v>3.763235569000244</v>
       </c>
       <c r="D45" t="n">
-        <v>4.078536748886108</v>
+        <v>3.698883533477783</v>
       </c>
       <c r="E45" t="n">
-        <v>4.164068460464478</v>
+        <v>3.6909019947052</v>
       </c>
       <c r="F45" t="n">
-        <v>3.983921051025391</v>
+        <v>3.709869146347046</v>
       </c>
       <c r="G45" t="n">
-        <v>4.261997938156128</v>
+        <v>3.801114559173584</v>
       </c>
       <c r="H45" t="n">
-        <v>3.92050838470459</v>
+        <v>3.882890939712524</v>
       </c>
       <c r="I45" t="n">
-        <v>3.95845627784729</v>
+        <v>3.651005744934082</v>
       </c>
       <c r="J45" t="n">
-        <v>4.00119423866272</v>
+        <v>3.654502630233765</v>
       </c>
       <c r="K45" t="n">
-        <v>4.101123571395874</v>
+        <v>4.212562799453735</v>
       </c>
       <c r="L45" t="n">
-        <v>4.068516516685486</v>
+        <v>3.784862422943115</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>4.28366231918335</v>
+        <v>4.105053663253784</v>
       </c>
       <c r="C46" t="n">
-        <v>4.601753950119019</v>
+        <v>4.24271821975708</v>
       </c>
       <c r="D46" t="n">
-        <v>4.414859533309937</v>
+        <v>4.035764455795288</v>
       </c>
       <c r="E46" t="n">
-        <v>4.528620481491089</v>
+        <v>4.424030065536499</v>
       </c>
       <c r="F46" t="n">
-        <v>4.34452223777771</v>
+        <v>4.74518609046936</v>
       </c>
       <c r="G46" t="n">
-        <v>3.977868556976318</v>
+        <v>4.173174619674683</v>
       </c>
       <c r="H46" t="n">
-        <v>4.54114294052124</v>
+        <v>4.010616779327393</v>
       </c>
       <c r="I46" t="n">
-        <v>4.563415765762329</v>
+        <v>4.06226921081543</v>
       </c>
       <c r="J46" t="n">
-        <v>4.121802806854248</v>
+        <v>3.983152866363525</v>
       </c>
       <c r="K46" t="n">
-        <v>4.301037073135376</v>
+        <v>4.254506826400757</v>
       </c>
       <c r="L46" t="n">
-        <v>4.367868566513062</v>
+        <v>4.20364727973938</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>4.293009757995605</v>
+        <v>3.943238973617554</v>
       </c>
       <c r="C47" t="n">
-        <v>4.258594751358032</v>
+        <v>3.921110153198242</v>
       </c>
       <c r="D47" t="n">
-        <v>4.390401840209961</v>
+        <v>4.212549448013306</v>
       </c>
       <c r="E47" t="n">
-        <v>4.424654483795166</v>
+        <v>4.262426614761353</v>
       </c>
       <c r="F47" t="n">
-        <v>4.274039030075073</v>
+        <v>4.472875118255615</v>
       </c>
       <c r="G47" t="n">
-        <v>4.245390653610229</v>
+        <v>4.128259181976318</v>
       </c>
       <c r="H47" t="n">
-        <v>4.977867364883423</v>
+        <v>4.96087121963501</v>
       </c>
       <c r="I47" t="n">
-        <v>4.166033029556274</v>
+        <v>4.472158193588257</v>
       </c>
       <c r="J47" t="n">
-        <v>4.466995239257812</v>
+        <v>4.790855646133423</v>
       </c>
       <c r="K47" t="n">
-        <v>4.883125066757202</v>
+        <v>4.422414064407349</v>
       </c>
       <c r="L47" t="n">
-        <v>4.438011121749878</v>
+        <v>4.358675861358643</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>4.126378536224365</v>
+        <v>4.821466684341431</v>
       </c>
       <c r="C48" t="n">
-        <v>4.398578882217407</v>
+        <v>4.504160165786743</v>
       </c>
       <c r="D48" t="n">
-        <v>4.385241746902466</v>
+        <v>4.342254877090454</v>
       </c>
       <c r="E48" t="n">
-        <v>4.405476808547974</v>
+        <v>4.312970876693726</v>
       </c>
       <c r="F48" t="n">
-        <v>4.36301064491272</v>
+        <v>4.924957513809204</v>
       </c>
       <c r="G48" t="n">
-        <v>4.273238897323608</v>
+        <v>4.312530755996704</v>
       </c>
       <c r="H48" t="n">
-        <v>4.400042533874512</v>
+        <v>4.004190921783447</v>
       </c>
       <c r="I48" t="n">
-        <v>4.795576810836792</v>
+        <v>4.802323341369629</v>
       </c>
       <c r="J48" t="n">
-        <v>4.281416893005371</v>
+        <v>4.273784160614014</v>
       </c>
       <c r="K48" t="n">
-        <v>4.170579195022583</v>
+        <v>4.672617435455322</v>
       </c>
       <c r="L48" t="n">
-        <v>4.359954094886779</v>
+        <v>4.497125673294067</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>4.472252130508423</v>
+        <v>4.529970169067383</v>
       </c>
       <c r="C49" t="n">
-        <v>4.440260648727417</v>
+        <v>4.486234188079834</v>
       </c>
       <c r="D49" t="n">
-        <v>4.49173378944397</v>
+        <v>4.256123304367065</v>
       </c>
       <c r="E49" t="n">
-        <v>4.753693103790283</v>
+        <v>4.32776141166687</v>
       </c>
       <c r="F49" t="n">
-        <v>4.412622451782227</v>
+        <v>4.577589511871338</v>
       </c>
       <c r="G49" t="n">
-        <v>4.324538707733154</v>
+        <v>4.556556463241577</v>
       </c>
       <c r="H49" t="n">
-        <v>4.644939422607422</v>
+        <v>4.99534797668457</v>
       </c>
       <c r="I49" t="n">
-        <v>4.746488332748413</v>
+        <v>4.436185836791992</v>
       </c>
       <c r="J49" t="n">
-        <v>4.519705057144165</v>
+        <v>4.619565725326538</v>
       </c>
       <c r="K49" t="n">
-        <v>5.012115716934204</v>
+        <v>4.406785488128662</v>
       </c>
       <c r="L49" t="n">
-        <v>4.581834936141968</v>
+        <v>4.519212007522583</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>3.489265441894531</v>
+        <v>3.365135192871094</v>
       </c>
       <c r="C50" t="n">
-        <v>3.467629909515381</v>
+        <v>3.44005823135376</v>
       </c>
       <c r="D50" t="n">
-        <v>3.661939382553101</v>
+        <v>3.27399730682373</v>
       </c>
       <c r="E50" t="n">
-        <v>3.624380588531494</v>
+        <v>3.627580642700195</v>
       </c>
       <c r="F50" t="n">
-        <v>3.524071931838989</v>
+        <v>3.472963094711304</v>
       </c>
       <c r="G50" t="n">
-        <v>3.609161615371704</v>
+        <v>3.368369817733765</v>
       </c>
       <c r="H50" t="n">
-        <v>3.544049501419067</v>
+        <v>3.839247941970825</v>
       </c>
       <c r="I50" t="n">
-        <v>3.454289197921753</v>
+        <v>3.561954021453857</v>
       </c>
       <c r="J50" t="n">
-        <v>4.03240442276001</v>
+        <v>3.415305376052856</v>
       </c>
       <c r="K50" t="n">
-        <v>3.580753326416016</v>
+        <v>3.591860294342041</v>
       </c>
       <c r="L50" t="n">
-        <v>3.598794531822205</v>
+        <v>3.495647192001343</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>4.298125028610229</v>
+        <v>3.95692253112793</v>
       </c>
       <c r="C51" t="n">
-        <v>4.181348085403442</v>
+        <v>3.941792726516724</v>
       </c>
       <c r="D51" t="n">
-        <v>4.376028060913086</v>
+        <v>4.072923421859741</v>
       </c>
       <c r="E51" t="n">
-        <v>4.595534563064575</v>
+        <v>4.07738995552063</v>
       </c>
       <c r="F51" t="n">
-        <v>4.169721126556396</v>
+        <v>4.78620457649231</v>
       </c>
       <c r="G51" t="n">
-        <v>4.401843786239624</v>
+        <v>4.614991903305054</v>
       </c>
       <c r="H51" t="n">
-        <v>4.231962203979492</v>
+        <v>3.982647895812988</v>
       </c>
       <c r="I51" t="n">
-        <v>4.007454395294189</v>
+        <v>4.358152151107788</v>
       </c>
       <c r="J51" t="n">
-        <v>4.170308113098145</v>
+        <v>4.086892366409302</v>
       </c>
       <c r="K51" t="n">
-        <v>4.387696504592896</v>
+        <v>4.148245096206665</v>
       </c>
       <c r="L51" t="n">
-        <v>4.282002186775207</v>
+        <v>4.202616262435913</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4.235087575912476</v>
+        <v>4.21017771244049</v>
       </c>
       <c r="C52" t="n">
-        <v>4.320180587768554</v>
+        <v>4.252398719787598</v>
       </c>
       <c r="D52" t="n">
-        <v>4.327541065216065</v>
+        <v>4.334375596046447</v>
       </c>
       <c r="E52" t="n">
-        <v>4.370893459320069</v>
+        <v>4.381525449752807</v>
       </c>
       <c r="F52" t="n">
-        <v>4.274174637794495</v>
+        <v>4.32588755607605</v>
       </c>
       <c r="G52" t="n">
-        <v>4.248413076400757</v>
+        <v>4.230918445587158</v>
       </c>
       <c r="H52" t="n">
-        <v>4.294649972915649</v>
+        <v>4.287704782485962</v>
       </c>
       <c r="I52" t="n">
-        <v>4.342207889556885</v>
+        <v>4.265911688804627</v>
       </c>
       <c r="J52" t="n">
-        <v>4.267722334861755</v>
+        <v>4.3805890417099</v>
       </c>
       <c r="K52" t="n">
-        <v>4.343227062225342</v>
+        <v>4.292798972129821</v>
       </c>
       <c r="L52" t="n">
-        <v>4.302409766197204</v>
+        <v>4.296228796482087</v>
       </c>
     </row>
   </sheetData>
